--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9502</v>
+        <v>0.9796</v>
       </c>
       <c r="F2" t="n">
-        <v>125.3302</v>
+        <v>86.7587</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>242.922</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9837</v>
+        <v>0.9711</v>
       </c>
       <c r="F3" t="n">
-        <v>82.1743</v>
+        <v>101.0696</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>243.3102</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9774</v>
+        <v>0.9775</v>
       </c>
       <c r="F4" t="n">
-        <v>93.67149999999999</v>
+        <v>94.026</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>265.9517</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.873</v>
+        <v>0.8739</v>
       </c>
       <c r="F5" t="n">
-        <v>218.795</v>
+        <v>218.5961</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>363.3764</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8425</v>
+        <v>0.8438</v>
       </c>
       <c r="F6" t="n">
-        <v>232.6314</v>
+        <v>232.3914</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>363.0053</v>
       </c>
     </row>
     <row r="7">
@@ -614,17 +614,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9728</v>
+        <v>0.9727</v>
       </c>
       <c r="F7" t="n">
-        <v>94.8847</v>
+        <v>94.9148</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>263.0181</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9696</v>
+        <v>0.979</v>
       </c>
       <c r="F8" t="n">
-        <v>98.85599999999999</v>
+        <v>83.9616</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>248.1219</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9845</v>
+        <v>0.9843</v>
       </c>
       <c r="F9" t="n">
-        <v>74.072</v>
+        <v>73.8614</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>233.6199</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9777</v>
       </c>
       <c r="F10" t="n">
-        <v>79.36320000000001</v>
+        <v>85.3206</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>246.7607</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9711</v>
+        <v>0.9706</v>
       </c>
       <c r="F11" t="n">
-        <v>97.5594</v>
+        <v>97.871</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>245.7767</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9811</v>
+        <v>0.9777</v>
       </c>
       <c r="F12" t="n">
-        <v>79.9435</v>
+        <v>84.45440000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>245.8881</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9813</v>
+        <v>0.9606</v>
       </c>
       <c r="F13" t="n">
-        <v>78.91500000000001</v>
+        <v>110.8643</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>246.4312</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9776</v>
+        <v>0.9706</v>
       </c>
       <c r="F14" t="n">
-        <v>85.64919999999999</v>
+        <v>98.3146</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>246.8296</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9708</v>
+        <v>0.9791</v>
       </c>
       <c r="F15" t="n">
-        <v>97.3419</v>
+        <v>82.43680000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>245.1536</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9815</v>
+        <v>0.9795</v>
       </c>
       <c r="F16" t="n">
-        <v>78.6981</v>
+        <v>81.6502</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>244.9911</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9715</v>
+        <v>0.9711</v>
       </c>
       <c r="F17" t="n">
-        <v>96.7364</v>
+        <v>96.6914</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>244.5361</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9653</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>100.9458</v>
+        <v>109.9168</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>240.9008</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9789</v>
+        <v>0.9787</v>
       </c>
       <c r="F19" t="n">
-        <v>83.2144</v>
+        <v>83.5843</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>235.9899</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>129.2121</v>
+        <v>99.3426</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>237.3937</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9417</v>
+        <v>0.9453</v>
       </c>
       <c r="F21" t="n">
-        <v>127.5055</v>
+        <v>124.7277</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>232.8284</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9792</v>
+        <v>0.9645</v>
       </c>
       <c r="F22" t="n">
-        <v>81.083</v>
+        <v>101.7267</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>240.742</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9574</v>
+        <v>0.9573</v>
       </c>
       <c r="F23" t="n">
-        <v>112.6571</v>
+        <v>112.6289</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>242.5427</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.959</v>
+        <v>0.9588</v>
       </c>
       <c r="F24" t="n">
-        <v>112.0086</v>
+        <v>112.4172</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>243.615</v>
       </c>
     </row>
     <row r="25">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9614</v>
+        <v>0.9616</v>
       </c>
       <c r="F25" t="n">
-        <v>106.7773</v>
+        <v>106.5943</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>242.4349</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.981</v>
       </c>
       <c r="F26" t="n">
-        <v>99.4829</v>
+        <v>83.94840000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>245.7808</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9774</v>
+        <v>0.9772</v>
       </c>
       <c r="F27" t="n">
-        <v>88.01900000000001</v>
+        <v>88.2679</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>241.6203</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9769</v>
+        <v>0.9774</v>
       </c>
       <c r="F28" t="n">
-        <v>86.80410000000001</v>
+        <v>85.38630000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>235.6195</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9676</v>
+        <v>0.9687</v>
       </c>
       <c r="F29" t="n">
-        <v>98.3297</v>
+        <v>97.7431</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>236.7572</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.968</v>
+        <v>0.9679</v>
       </c>
       <c r="F30" t="n">
-        <v>99.73480000000001</v>
+        <v>99.9156</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>236.5194</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9796</v>
+        <v>0.9379</v>
       </c>
       <c r="F31" t="n">
-        <v>80.9415</v>
+        <v>129.9549</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>234.7886</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9774</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>83.0192</v>
+        <v>81.84050000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>232.2462</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9648</v>
+        <v>0.981</v>
       </c>
       <c r="F33" t="n">
-        <v>102.356</v>
+        <v>79.1925</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>236.138</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9791</v>
+        <v>0.9789</v>
       </c>
       <c r="F34" t="n">
-        <v>84.2299</v>
+        <v>85.002</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>225.4402</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>71.5282</v>
+        <v>85.3811</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>221.3179</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9865</v>
+        <v>0.9868</v>
       </c>
       <c r="F36" t="n">
-        <v>75.0158</v>
+        <v>74.94370000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>229.803</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.985</v>
+        <v>0.984</v>
       </c>
       <c r="F37" t="n">
-        <v>75.3399</v>
+        <v>74.2026</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>233.2675</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9858</v>
+        <v>0.9862</v>
       </c>
       <c r="F38" t="n">
-        <v>72.4603</v>
+        <v>71.9222</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>228.5267</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9709</v>
+        <v>0.9707</v>
       </c>
       <c r="F39" t="n">
-        <v>99.6092</v>
+        <v>99.6294</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>236.679</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9705</v>
+        <v>0.97</v>
       </c>
       <c r="F40" t="n">
-        <v>100.1633</v>
+        <v>100.6551</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>240.2132</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9799</v>
+        <v>0.9787</v>
       </c>
       <c r="F41" t="n">
-        <v>83.99809999999999</v>
+        <v>85.07940000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>225.965</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9845</v>
+        <v>0.9771</v>
       </c>
       <c r="F42" t="n">
-        <v>71.2499</v>
+        <v>87.5274</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>221.6226</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9865</v>
+        <v>0.9866</v>
       </c>
       <c r="F43" t="n">
-        <v>75.90689999999999</v>
+        <v>76.1677</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>233.718</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>0.9858</v>
       </c>
       <c r="F44" t="n">
-        <v>73.241</v>
+        <v>72.6203</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>234.3743</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9848</v>
+        <v>0.9853</v>
       </c>
       <c r="F45" t="n">
-        <v>74.5244</v>
+        <v>74.0673</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>230.9389</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9705</v>
+        <v>0.9702</v>
       </c>
       <c r="F46" t="n">
-        <v>101.4162</v>
+        <v>101.3525</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>241.0197</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9715</v>
+        <v>0.971</v>
       </c>
       <c r="F47" t="n">
-        <v>99.96810000000001</v>
+        <v>100.1909</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>239.1284</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.986</v>
+        <v>0.9855</v>
       </c>
       <c r="F48" t="n">
-        <v>77.2636</v>
+        <v>78.039</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>233.5794</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9839</v>
+        <v>0.9738</v>
       </c>
       <c r="F49" t="n">
-        <v>77.49590000000001</v>
+        <v>95.00490000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>232.5281</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9143</v>
+        <v>0.9152</v>
       </c>
       <c r="F50" t="n">
-        <v>205.6374</v>
+        <v>205.4592</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>348.5644</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8499</v>
+        <v>0.8498</v>
       </c>
       <c r="F51" t="n">
-        <v>237.0494</v>
+        <v>237.0721</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>349.958</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8747</v>
+        <v>0.8753</v>
       </c>
       <c r="F52" t="n">
-        <v>218.8069</v>
+        <v>218.7054</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>350.4963</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9077</v>
+        <v>0.9076</v>
       </c>
       <c r="F53" t="n">
-        <v>206.9495</v>
+        <v>206.9783</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>333.6465</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>0.8977000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>207.1186</v>
+        <v>207.1178</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>327.3914</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>0.8699</v>
       </c>
       <c r="F55" t="n">
-        <v>232.6323</v>
+        <v>232.6325</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>352.4195</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8828</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>231.1191</v>
+        <v>231.1333</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>351.6996</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9503</v>
+        <v>0.9494</v>
       </c>
       <c r="F57" t="n">
-        <v>165.7486</v>
+        <v>166.213</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>349.096</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.845</v>
+        <v>0.8471</v>
       </c>
       <c r="F58" t="n">
-        <v>231.9561</v>
+        <v>231.5552</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>363.8753</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8399</v>
+        <v>0.8424</v>
       </c>
       <c r="F59" t="n">
-        <v>233.7277</v>
+        <v>233.443</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>363.2236</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.834</v>
+        <v>0.8364</v>
       </c>
       <c r="F60" t="n">
-        <v>234.1094</v>
+        <v>233.6898</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>362.2392</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8277</v>
+        <v>0.8306</v>
       </c>
       <c r="F61" t="n">
-        <v>235.8933</v>
+        <v>235.3027</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>362.3811</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8681</v>
+        <v>0.8685</v>
       </c>
       <c r="F62" t="n">
-        <v>228.5327</v>
+        <v>228.4433</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>359.6111</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8439</v>
+        <v>0.8436</v>
       </c>
       <c r="F63" t="n">
-        <v>239.1744</v>
+        <v>239.271</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>359.0133</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8455</v>
+        <v>0.845</v>
       </c>
       <c r="F64" t="n">
-        <v>239.0859</v>
+        <v>239.2279</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>359.2642</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8391</v>
+        <v>0.839</v>
       </c>
       <c r="F65" t="n">
-        <v>239.9655</v>
+        <v>240.0046</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>358.2305</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8923</v>
+        <v>0.8925</v>
       </c>
       <c r="F66" t="n">
-        <v>221.1089</v>
+        <v>221.0742</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>350.796</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>0.8695000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>232.5771</v>
+        <v>232.5881</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>349.9968</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8675</v>
+        <v>0.8673</v>
       </c>
       <c r="F68" t="n">
-        <v>233.3865</v>
+        <v>233.4053</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>352.0432</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.982</v>
       </c>
       <c r="F69" t="n">
-        <v>83.26130000000001</v>
+        <v>81.91079999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>236.6896</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.981</v>
+        <v>0.9804</v>
       </c>
       <c r="F70" t="n">
-        <v>82.53</v>
+        <v>82.642</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>239.2909</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>0.9797</v>
       </c>
       <c r="F71" t="n">
-        <v>84.86</v>
+        <v>84.39830000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>237.2127</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9778</v>
+        <v>0.9786</v>
       </c>
       <c r="F72" t="n">
-        <v>87.92310000000001</v>
+        <v>85.8901</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>237.4455</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9826</v>
+        <v>0.983</v>
       </c>
       <c r="F73" t="n">
-        <v>79.96299999999999</v>
+        <v>77.65940000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>234.7998</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9741</v>
+        <v>0.9729</v>
       </c>
       <c r="F74" t="n">
-        <v>91.6622</v>
+        <v>91.9653</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>234.3634</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.955</v>
+        <v>0.9755</v>
       </c>
       <c r="F75" t="n">
-        <v>118.6925</v>
+        <v>90.1386</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>256.3623</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.955</v>
+        <v>0.9755</v>
       </c>
       <c r="F76" t="n">
-        <v>118.6925</v>
+        <v>90.1386</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>256.3623</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8435</v>
+        <v>0.844</v>
       </c>
       <c r="F77" t="n">
-        <v>232.888</v>
+        <v>232.6765</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>365.2175</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8013</v>
+        <v>0.8243</v>
       </c>
       <c r="F78" t="n">
-        <v>250.9794</v>
+        <v>242.4358</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>366.9045</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8022</v>
+        <v>0.802</v>
       </c>
       <c r="F79" t="n">
-        <v>250.9232</v>
+        <v>250.8977</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>366.5335</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8006</v>
+        <v>0.8004</v>
       </c>
       <c r="F80" t="n">
-        <v>250.9929</v>
+        <v>250.9858</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>366.8683</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8549</v>
+        <v>0.8552</v>
       </c>
       <c r="F81" t="n">
-        <v>236.22</v>
+        <v>236.1438</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>354.1679</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8545</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="F82" t="n">
-        <v>235.0888</v>
+        <v>235.1017</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>354.2557</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9748</v>
       </c>
       <c r="F83" t="n">
-        <v>119.8625</v>
+        <v>90.7975</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>256.2721</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.954</v>
+        <v>0.974</v>
       </c>
       <c r="F84" t="n">
-        <v>119.7108</v>
+        <v>91.16540000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>255.1345</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9548</v>
+        <v>0.975</v>
       </c>
       <c r="F85" t="n">
-        <v>119.0961</v>
+        <v>90.8227</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>256.5464</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9781</v>
+        <v>0.9787</v>
       </c>
       <c r="F86" t="n">
-        <v>88.0757</v>
+        <v>84.4542</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>245.5629</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9786</v>
+        <v>0.9788</v>
       </c>
       <c r="F87" t="n">
-        <v>87.2136</v>
+        <v>86.7581</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>245.9053</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9667</v>
+        <v>0.967</v>
       </c>
       <c r="F88" t="n">
-        <v>101.4035</v>
+        <v>100.7658</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>238.6303</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
         <v>0.9665</v>
       </c>
       <c r="F89" t="n">
-        <v>101.7319</v>
+        <v>101.7578</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>240.5505</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9839</v>
+        <v>0.9866</v>
       </c>
       <c r="F90" t="n">
-        <v>77.2967</v>
+        <v>76.1592</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>233.8439</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
         <v>0.9858</v>
       </c>
       <c r="F91" t="n">
-        <v>73.241</v>
+        <v>72.6203</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>234.5405</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9667</v>
+        <v>0.967</v>
       </c>
       <c r="F92" t="n">
-        <v>101.4035</v>
+        <v>100.7658</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>238.6303</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>0.9858</v>
       </c>
       <c r="F93" t="n">
-        <v>73.241</v>
+        <v>72.6203</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>234.5405</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9774</v>
+        <v>0.9775</v>
       </c>
       <c r="F94" t="n">
-        <v>93.67149999999999</v>
+        <v>94.026</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>265.9517</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.75</v>
+        <v>0.7496</v>
       </c>
       <c r="F95" t="n">
-        <v>264.5473</v>
+        <v>264.5763</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>381.9164</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9785</v>
+        <v>0.9789</v>
       </c>
       <c r="F96" t="n">
-        <v>92.34699999999999</v>
+        <v>91.86360000000001</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>268.7021</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9781</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F97" t="n">
-        <v>92.98909999999999</v>
+        <v>92.9584</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>268.7802</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9818</v>
+        <v>0.9822</v>
       </c>
       <c r="F98" t="n">
-        <v>81.88249999999999</v>
+        <v>81.31399999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>237.6991</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9628</v>
+        <v>0.9626</v>
       </c>
       <c r="F99" t="n">
-        <v>107.7686</v>
+        <v>107.9401</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>235.3773</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9804</v>
+        <v>0.9801</v>
       </c>
       <c r="F100" t="n">
-        <v>82.93640000000001</v>
+        <v>83.2572</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>236.8634</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9596</v>
+        <v>0.9595</v>
       </c>
       <c r="F101" t="n">
-        <v>111.6937</v>
+        <v>111.5956</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>237.6393</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9587</v>
+        <v>0.9586</v>
       </c>
       <c r="F102" t="n">
-        <v>112.0423</v>
+        <v>112.3118</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>240.2865</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9825</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F103" t="n">
-        <v>81.61450000000001</v>
+        <v>81.9766</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>238.4081</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E104" t="n">
         <v>0.9815</v>
       </c>
       <c r="F104" t="n">
-        <v>83.2102</v>
+        <v>83.1315</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>238.4114</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9805</v>
+        <v>0.9804</v>
       </c>
       <c r="F105" t="n">
-        <v>81.66589999999999</v>
+        <v>83.352</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>236.7661</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9636</v>
       </c>
       <c r="F106" t="n">
-        <v>107.0544</v>
+        <v>106.9045</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>236.9577</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9606</v>
+        <v>0.9604</v>
       </c>
       <c r="F107" t="n">
-        <v>109.9612</v>
+        <v>110.0998</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>237.7197</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9823</v>
+        <v>0.9825</v>
       </c>
       <c r="F108" t="n">
-        <v>84.0342</v>
+        <v>83.64319999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>240.3379</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9741</v>
+        <v>0.9747</v>
       </c>
       <c r="F109" t="n">
-        <v>92.9858</v>
+        <v>90.88120000000001</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>228.8701</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9817</v>
+        <v>0.9823</v>
       </c>
       <c r="F110" t="n">
-        <v>81.2039</v>
+        <v>80.6255</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>234.7608</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9817</v>
       </c>
       <c r="F111" t="n">
-        <v>81.88930000000001</v>
+        <v>81.04940000000001</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>233.2302</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9821</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>84.04049999999999</v>
+        <v>83.53700000000001</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>240.37</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.974</v>
+        <v>0.9745</v>
       </c>
       <c r="F113" t="n">
-        <v>93.1373</v>
+        <v>91.33159999999999</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>228.6304</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9832</v>
+        <v>0.977</v>
       </c>
       <c r="F114" t="n">
-        <v>79.2955</v>
+        <v>85.42910000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>232.7535</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9827</v>
+        <v>0.9828</v>
       </c>
       <c r="F115" t="n">
-        <v>80.14490000000001</v>
+        <v>79.4413</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>231.3174</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9301</v>
+        <v>0.9304</v>
       </c>
       <c r="F116" t="n">
-        <v>180.407</v>
+        <v>180.5158</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>356.6879</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8524</v>
+        <v>0.8527</v>
       </c>
       <c r="F117" t="n">
-        <v>226.3928</v>
+        <v>226.2557</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>354.6575</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9805</v>
+        <v>0.9804</v>
       </c>
       <c r="F118" t="n">
-        <v>81.66589999999999</v>
+        <v>83.352</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>236.7661</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.974</v>
+        <v>0.9745</v>
       </c>
       <c r="F119" t="n">
-        <v>93.1373</v>
+        <v>91.33159999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>228.6304</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8963</v>
+        <v>0.8964</v>
       </c>
       <c r="F120" t="n">
-        <v>162.1669</v>
+        <v>162.0505</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>253.4733</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8963</v>
+        <v>0.8964</v>
       </c>
       <c r="F121" t="n">
-        <v>162.1669</v>
+        <v>162.0505</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>253.4733</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9228</v>
+        <v>0.9366</v>
       </c>
       <c r="F122" t="n">
-        <v>145.0143</v>
+        <v>134.4979</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>239.2284</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.974</v>
+        <v>0.9823</v>
       </c>
       <c r="F123" t="n">
-        <v>93.154</v>
+        <v>78.7385</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>228.6513</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.982</v>
+        <v>0.9816</v>
       </c>
       <c r="F124" t="n">
-        <v>80.9212</v>
+        <v>80.99630000000001</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>232.0748</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9442</v>
       </c>
       <c r="F125" t="n">
-        <v>134.0662</v>
+        <v>133.9448</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>270.8245</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9811</v>
+        <v>0.9823</v>
       </c>
       <c r="F126" t="n">
-        <v>84.33540000000001</v>
+        <v>83.3531</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>251.5898</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8566</v>
+        <v>0.8561</v>
       </c>
       <c r="F127" t="n">
-        <v>223.8895</v>
+        <v>223.916</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>363.3514</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9806</v>
+        <v>0.9811</v>
       </c>
       <c r="F128" t="n">
-        <v>83.90470000000001</v>
+        <v>83.87</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>251.4823</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9813</v>
+        <v>0.9821</v>
       </c>
       <c r="F129" t="n">
-        <v>82.12730000000001</v>
+        <v>81.5492</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>254.2119</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9806</v>
+        <v>0.9808</v>
       </c>
       <c r="F130" t="n">
-        <v>84.78019999999999</v>
+        <v>85.2962</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>250.5</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.98</v>
+        <v>0.9809</v>
       </c>
       <c r="F131" t="n">
-        <v>84.435</v>
+        <v>84.0433</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>250.5492</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9821</v>
+        <v>0.9825</v>
       </c>
       <c r="F132" t="n">
-        <v>82.5855</v>
+        <v>82.889</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>248.7274</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9818</v>
+        <v>0.9819</v>
       </c>
       <c r="F133" t="n">
-        <v>82.83</v>
+        <v>82.7163</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>248.52</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9812</v>
+        <v>0.9807</v>
       </c>
       <c r="F134" t="n">
-        <v>83.3822</v>
+        <v>84.7068</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>249.7361</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.981</v>
+        <v>0.9815</v>
       </c>
       <c r="F135" t="n">
-        <v>84.3741</v>
+        <v>83.97029999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>251.0583</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9811</v>
+        <v>0.9816</v>
       </c>
       <c r="F136" t="n">
-        <v>82.9611</v>
+        <v>83.5458</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>250.333</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9608</v>
+        <v>0.9611</v>
       </c>
       <c r="F137" t="n">
-        <v>109.4637</v>
+        <v>109.0518</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>240.8848</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9701</v>
       </c>
       <c r="F138" t="n">
-        <v>81.9729</v>
+        <v>99.7942</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>242.6957</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9698</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>97.79340000000001</v>
+        <v>99.108</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>241.9638</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9698</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>93.6722</v>
+        <v>91.4914</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>225.1426</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9775</v>
+        <v>0.9801</v>
       </c>
       <c r="F141" t="n">
-        <v>81.51439999999999</v>
+        <v>82.8646</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>232.2176</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9701</v>
       </c>
       <c r="F142" t="n">
-        <v>81.9729</v>
+        <v>99.7942</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>242.6957</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9707</v>
+        <v>0.9706</v>
       </c>
       <c r="F143" t="n">
-        <v>96.14449999999999</v>
+        <v>95.77119999999999</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>234.0818</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9712</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F144" t="n">
-        <v>96.4873</v>
+        <v>96.3704</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>239.2396</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9775</v>
+        <v>0.9801</v>
       </c>
       <c r="F145" t="n">
-        <v>81.51439999999999</v>
+        <v>82.8646</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>232.2176</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8401</v>
+        <v>0.8397</v>
       </c>
       <c r="F146" t="n">
-        <v>232.193</v>
+        <v>232.145</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>361.626</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.8376</v>
+        <v>0.8375</v>
       </c>
       <c r="F147" t="n">
-        <v>232.8674</v>
+        <v>232.6473</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>361.7929</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8357</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="F148" t="n">
-        <v>232.6148</v>
+        <v>232.3384</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>361.3305</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8387</v>
+        <v>0.8649</v>
       </c>
       <c r="F149" t="n">
-        <v>232.4086</v>
+        <v>221.077</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>360.8039</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8371</v>
+        <v>0.836</v>
       </c>
       <c r="F150" t="n">
-        <v>231.7813</v>
+        <v>231.8782</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>363.0733</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8395</v>
+        <v>0.8386</v>
       </c>
       <c r="F151" t="n">
-        <v>230.6981</v>
+        <v>230.8075</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>361.7634</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8416</v>
+        <v>0.8406</v>
       </c>
       <c r="F152" t="n">
-        <v>230.7178</v>
+        <v>230.8476</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>361.4492</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8366</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="F153" t="n">
-        <v>232.8341</v>
+        <v>232.9255</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>362.5899</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8346</v>
+        <v>0.8344</v>
       </c>
       <c r="F154" t="n">
-        <v>231.7734</v>
+        <v>231.8489</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>360.9492</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E155" t="n">
         <v>0.8764</v>
       </c>
       <c r="F155" t="n">
-        <v>228.2185</v>
+        <v>228.2008</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>359.2558</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
         <v>0.8505</v>
       </c>
       <c r="F156" t="n">
-        <v>238.8993</v>
+        <v>238.8687</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>360.2218</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8758</v>
+        <v>0.8759</v>
       </c>
       <c r="F157" t="n">
-        <v>227.4409</v>
+        <v>227.3839</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>359.1725</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8746</v>
+        <v>0.8742</v>
       </c>
       <c r="F158" t="n">
-        <v>230.0161</v>
+        <v>230.0989</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>346.9333</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9767</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="F159" t="n">
-        <v>85.0819</v>
+        <v>84.96429999999999</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>240.4694</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8456</v>
+        <v>0.8462</v>
       </c>
       <c r="F160" t="n">
-        <v>242.5766</v>
+        <v>242.6177</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>362.46</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8583</v>
+        <v>0.8581</v>
       </c>
       <c r="F161" t="n">
-        <v>230.9976</v>
+        <v>231.0193</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>361.4839</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9609</v>
       </c>
       <c r="F162" t="n">
-        <v>108.7036</v>
+        <v>109.176</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>243.5304</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9709</v>
+        <v>0.9712</v>
       </c>
       <c r="F163" t="n">
-        <v>97.2136</v>
+        <v>96.669</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>248.084</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9698</v>
+        <v>0.9712</v>
       </c>
       <c r="F164" t="n">
-        <v>93.6803</v>
+        <v>91.63760000000001</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>224.8966</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9442</v>
       </c>
       <c r="F165" t="n">
-        <v>134.0662</v>
+        <v>133.9448</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>270.8245</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7457</v>
+        <v>0.7458</v>
       </c>
       <c r="F166" t="n">
-        <v>265.673</v>
+        <v>265.7293</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>381.6626</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9739</v>
+        <v>0.9722</v>
       </c>
       <c r="F167" t="n">
-        <v>90.9365</v>
+        <v>92.24890000000001</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>222.8232</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9786</v>
+        <v>0.9791</v>
       </c>
       <c r="F168" t="n">
-        <v>78.696</v>
+        <v>77.5085</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>218.4699</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9686</v>
+        <v>0.9534</v>
       </c>
       <c r="F169" t="n">
-        <v>97.9355</v>
+        <v>122.3717</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>246.8227</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9828</v>
+        <v>0.9804</v>
       </c>
       <c r="F170" t="n">
-        <v>81.18680000000001</v>
+        <v>82.3142</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>238.2644</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9842</v>
+        <v>0.9839</v>
       </c>
       <c r="F171" t="n">
-        <v>76.91970000000001</v>
+        <v>76.9773</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>228.941</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9684</v>
+        <v>0.9683</v>
       </c>
       <c r="F172" t="n">
-        <v>98.7687</v>
+        <v>98.7353</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>238.3591</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9796</v>
       </c>
       <c r="F2" t="n">
+        <v>1.4754</v>
+      </c>
+      <c r="G2" t="n">
         <v>86.7587</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>242.922</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9711</v>
       </c>
       <c r="F3" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="G3" t="n">
         <v>101.0696</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>243.3102</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9775</v>
       </c>
       <c r="F4" t="n">
+        <v>1.5698</v>
+      </c>
+      <c r="G4" t="n">
         <v>94.026</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>265.9517</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.8739</v>
       </c>
       <c r="F5" t="n">
+        <v>2.0638</v>
+      </c>
+      <c r="G5" t="n">
         <v>218.5961</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>363.3764</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.8438</v>
       </c>
       <c r="F6" t="n">
+        <v>2.0616</v>
+      </c>
+      <c r="G6" t="n">
         <v>232.3914</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>363.0053</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.9727</v>
       </c>
       <c r="F7" t="n">
+        <v>1.5573</v>
+      </c>
+      <c r="G7" t="n">
         <v>94.9148</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>263.0181</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.979</v>
       </c>
       <c r="F8" t="n">
+        <v>1.496</v>
+      </c>
+      <c r="G8" t="n">
         <v>83.9616</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>248.1219</v>
       </c>
     </row>
@@ -679,9 +705,12 @@
         <v>0.9843</v>
       </c>
       <c r="F9" t="n">
+        <v>1.4397</v>
+      </c>
+      <c r="G9" t="n">
         <v>73.8614</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>233.6199</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.9777</v>
       </c>
       <c r="F10" t="n">
+        <v>1.4906</v>
+      </c>
+      <c r="G10" t="n">
         <v>85.3206</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>246.7607</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.9706</v>
       </c>
       <c r="F11" t="n">
+        <v>1.4867</v>
+      </c>
+      <c r="G11" t="n">
         <v>97.871</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>245.7767</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.9777</v>
       </c>
       <c r="F12" t="n">
+        <v>1.4871</v>
+      </c>
+      <c r="G12" t="n">
         <v>84.45440000000001</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>245.8881</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9606</v>
       </c>
       <c r="F13" t="n">
+        <v>1.4893</v>
+      </c>
+      <c r="G13" t="n">
         <v>110.8643</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>246.4312</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.9706</v>
       </c>
       <c r="F14" t="n">
+        <v>1.4908</v>
+      </c>
+      <c r="G14" t="n">
         <v>98.3146</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>246.8296</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9791</v>
       </c>
       <c r="F15" t="n">
+        <v>1.4842</v>
+      </c>
+      <c r="G15" t="n">
         <v>82.43680000000001</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>245.1536</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.9795</v>
       </c>
       <c r="F16" t="n">
+        <v>1.4836</v>
+      </c>
+      <c r="G16" t="n">
         <v>81.6502</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>244.9911</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.9711</v>
       </c>
       <c r="F17" t="n">
+        <v>1.4818</v>
+      </c>
+      <c r="G17" t="n">
         <v>96.6914</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>244.5361</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9631999999999999</v>
       </c>
       <c r="F18" t="n">
+        <v>1.4676</v>
+      </c>
+      <c r="G18" t="n">
         <v>109.9168</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>240.9008</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9787</v>
       </c>
       <c r="F19" t="n">
+        <v>1.4487</v>
+      </c>
+      <c r="G19" t="n">
         <v>83.5843</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>235.9899</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9681999999999999</v>
       </c>
       <c r="F20" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="G20" t="n">
         <v>99.3426</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>237.3937</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9453</v>
       </c>
       <c r="F21" t="n">
+        <v>1.4367</v>
+      </c>
+      <c r="G21" t="n">
         <v>124.7277</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>232.8284</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9645</v>
       </c>
       <c r="F22" t="n">
+        <v>1.4669</v>
+      </c>
+      <c r="G22" t="n">
         <v>101.7267</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>240.742</v>
       </c>
     </row>
@@ -1085,9 +1153,12 @@
         <v>0.9573</v>
       </c>
       <c r="F23" t="n">
+        <v>1.4739</v>
+      </c>
+      <c r="G23" t="n">
         <v>112.6289</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>242.5427</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.9588</v>
       </c>
       <c r="F24" t="n">
+        <v>1.4781</v>
+      </c>
+      <c r="G24" t="n">
         <v>112.4172</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>243.615</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9616</v>
       </c>
       <c r="F25" t="n">
+        <v>1.4735</v>
+      </c>
+      <c r="G25" t="n">
         <v>106.5943</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>242.4349</v>
       </c>
     </row>
@@ -1172,9 +1249,12 @@
         <v>0.981</v>
       </c>
       <c r="F26" t="n">
+        <v>1.4867</v>
+      </c>
+      <c r="G26" t="n">
         <v>83.94840000000001</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>245.7808</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9772</v>
       </c>
       <c r="F27" t="n">
+        <v>1.4703</v>
+      </c>
+      <c r="G27" t="n">
         <v>88.2679</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>241.6203</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9774</v>
       </c>
       <c r="F28" t="n">
+        <v>1.4473</v>
+      </c>
+      <c r="G28" t="n">
         <v>85.38630000000001</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>235.6195</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9687</v>
       </c>
       <c r="F29" t="n">
+        <v>1.4516</v>
+      </c>
+      <c r="G29" t="n">
         <v>97.7431</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>236.7572</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9679</v>
       </c>
       <c r="F30" t="n">
+        <v>1.4507</v>
+      </c>
+      <c r="G30" t="n">
         <v>99.9156</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>236.5194</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9379</v>
       </c>
       <c r="F31" t="n">
+        <v>1.4441</v>
+      </c>
+      <c r="G31" t="n">
         <v>129.9549</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>234.7886</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F32" t="n">
+        <v>1.4346</v>
+      </c>
+      <c r="G32" t="n">
         <v>81.84050000000001</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>232.2462</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.981</v>
       </c>
       <c r="F33" t="n">
+        <v>1.4492</v>
+      </c>
+      <c r="G33" t="n">
         <v>79.1925</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>236.138</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9789</v>
       </c>
       <c r="F34" t="n">
+        <v>1.4095</v>
+      </c>
+      <c r="G34" t="n">
         <v>85.002</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>225.4402</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F35" t="n">
+        <v>1.3946</v>
+      </c>
+      <c r="G35" t="n">
         <v>85.3811</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>221.3179</v>
       </c>
     </row>
@@ -1462,9 +1569,12 @@
         <v>0.9868</v>
       </c>
       <c r="F36" t="n">
+        <v>1.4255</v>
+      </c>
+      <c r="G36" t="n">
         <v>74.94370000000001</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>229.803</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.984</v>
       </c>
       <c r="F37" t="n">
+        <v>1.4384</v>
+      </c>
+      <c r="G37" t="n">
         <v>74.2026</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>233.2675</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9862</v>
       </c>
       <c r="F38" t="n">
+        <v>1.4208</v>
+      </c>
+      <c r="G38" t="n">
         <v>71.9222</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>228.5267</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9707</v>
       </c>
       <c r="F39" t="n">
+        <v>1.4513</v>
+      </c>
+      <c r="G39" t="n">
         <v>99.6294</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>236.679</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.97</v>
       </c>
       <c r="F40" t="n">
+        <v>1.4649</v>
+      </c>
+      <c r="G40" t="n">
         <v>100.6551</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>240.2132</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9787</v>
       </c>
       <c r="F41" t="n">
+        <v>1.4114</v>
+      </c>
+      <c r="G41" t="n">
         <v>85.07940000000001</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>225.965</v>
       </c>
     </row>
@@ -1636,9 +1761,12 @@
         <v>0.9771</v>
       </c>
       <c r="F42" t="n">
+        <v>1.3957</v>
+      </c>
+      <c r="G42" t="n">
         <v>87.5274</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>221.6226</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9866</v>
       </c>
       <c r="F43" t="n">
+        <v>1.4401</v>
+      </c>
+      <c r="G43" t="n">
         <v>76.1677</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>233.718</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9858</v>
       </c>
       <c r="F44" t="n">
+        <v>1.4426</v>
+      </c>
+      <c r="G44" t="n">
         <v>72.6203</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>234.3743</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9853</v>
       </c>
       <c r="F45" t="n">
+        <v>1.4297</v>
+      </c>
+      <c r="G45" t="n">
         <v>74.0673</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>230.9389</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9702</v>
       </c>
       <c r="F46" t="n">
+        <v>1.468</v>
+      </c>
+      <c r="G46" t="n">
         <v>101.3525</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>241.0197</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.971</v>
       </c>
       <c r="F47" t="n">
+        <v>1.4607</v>
+      </c>
+      <c r="G47" t="n">
         <v>100.1909</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>239.1284</v>
       </c>
     </row>
@@ -1810,9 +1953,12 @@
         <v>0.9855</v>
       </c>
       <c r="F48" t="n">
+        <v>1.4396</v>
+      </c>
+      <c r="G48" t="n">
         <v>78.039</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>233.5794</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.9738</v>
       </c>
       <c r="F49" t="n">
+        <v>1.4356</v>
+      </c>
+      <c r="G49" t="n">
         <v>95.00490000000001</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>232.5281</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.9152</v>
       </c>
       <c r="F50" t="n">
+        <v>1.9789</v>
+      </c>
+      <c r="G50" t="n">
         <v>205.4592</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>348.5644</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.8498</v>
       </c>
       <c r="F51" t="n">
+        <v>1.9867</v>
+      </c>
+      <c r="G51" t="n">
         <v>237.0721</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>349.958</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.8753</v>
       </c>
       <c r="F52" t="n">
+        <v>1.9897</v>
+      </c>
+      <c r="G52" t="n">
         <v>218.7054</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>350.4963</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.9076</v>
       </c>
       <c r="F53" t="n">
+        <v>1.8969</v>
+      </c>
+      <c r="G53" t="n">
         <v>206.9783</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>333.6465</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.8977000000000001</v>
       </c>
       <c r="F54" t="n">
+        <v>1.8635</v>
+      </c>
+      <c r="G54" t="n">
         <v>207.1178</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>327.3914</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.8699</v>
       </c>
       <c r="F55" t="n">
+        <v>2.0006</v>
+      </c>
+      <c r="G55" t="n">
         <v>232.6325</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>352.4195</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.8826000000000001</v>
       </c>
       <c r="F56" t="n">
+        <v>1.9965</v>
+      </c>
+      <c r="G56" t="n">
         <v>231.1333</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>351.6996</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.9494</v>
       </c>
       <c r="F57" t="n">
+        <v>1.9818</v>
+      </c>
+      <c r="G57" t="n">
         <v>166.213</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>349.096</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.8471</v>
       </c>
       <c r="F58" t="n">
+        <v>2.0667</v>
+      </c>
+      <c r="G58" t="n">
         <v>231.5552</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>363.8753</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.8424</v>
       </c>
       <c r="F59" t="n">
+        <v>2.0629</v>
+      </c>
+      <c r="G59" t="n">
         <v>233.443</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>363.2236</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.8364</v>
       </c>
       <c r="F60" t="n">
+        <v>2.0572</v>
+      </c>
+      <c r="G60" t="n">
         <v>233.6898</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>362.2392</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.8306</v>
       </c>
       <c r="F61" t="n">
+        <v>2.058</v>
+      </c>
+      <c r="G61" t="n">
         <v>235.3027</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>362.3811</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.8685</v>
       </c>
       <c r="F62" t="n">
+        <v>2.0419</v>
+      </c>
+      <c r="G62" t="n">
         <v>228.4433</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>359.6111</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.8436</v>
       </c>
       <c r="F63" t="n">
+        <v>2.0384</v>
+      </c>
+      <c r="G63" t="n">
         <v>239.271</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>359.0133</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.845</v>
       </c>
       <c r="F64" t="n">
+        <v>2.0399</v>
+      </c>
+      <c r="G64" t="n">
         <v>239.2279</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>359.2642</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.839</v>
       </c>
       <c r="F65" t="n">
+        <v>2.0339</v>
+      </c>
+      <c r="G65" t="n">
         <v>240.0046</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>358.2305</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.8925</v>
       </c>
       <c r="F66" t="n">
+        <v>1.9914</v>
+      </c>
+      <c r="G66" t="n">
         <v>221.0742</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>350.796</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.8695000000000001</v>
       </c>
       <c r="F67" t="n">
+        <v>1.9869</v>
+      </c>
+      <c r="G67" t="n">
         <v>232.5881</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>349.9968</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.8673</v>
       </c>
       <c r="F68" t="n">
+        <v>1.9985</v>
+      </c>
+      <c r="G68" t="n">
         <v>233.4053</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>352.0432</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.982</v>
       </c>
       <c r="F69" t="n">
+        <v>1.4513</v>
+      </c>
+      <c r="G69" t="n">
         <v>81.91079999999999</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>236.6896</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9804</v>
       </c>
       <c r="F70" t="n">
+        <v>1.4613</v>
+      </c>
+      <c r="G70" t="n">
         <v>82.642</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>239.2909</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9797</v>
       </c>
       <c r="F71" t="n">
+        <v>1.4533</v>
+      </c>
+      <c r="G71" t="n">
         <v>84.39830000000001</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>237.2127</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9786</v>
       </c>
       <c r="F72" t="n">
+        <v>1.4542</v>
+      </c>
+      <c r="G72" t="n">
         <v>85.8901</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>237.4455</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.983</v>
       </c>
       <c r="F73" t="n">
+        <v>1.4442</v>
+      </c>
+      <c r="G73" t="n">
         <v>77.65940000000001</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>234.7998</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9729</v>
       </c>
       <c r="F74" t="n">
+        <v>1.4425</v>
+      </c>
+      <c r="G74" t="n">
         <v>91.9653</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>234.3634</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9755</v>
       </c>
       <c r="F75" t="n">
+        <v>1.5295</v>
+      </c>
+      <c r="G75" t="n">
         <v>90.1386</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>256.3623</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9755</v>
       </c>
       <c r="F76" t="n">
+        <v>1.5295</v>
+      </c>
+      <c r="G76" t="n">
         <v>90.1386</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>256.3623</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.844</v>
       </c>
       <c r="F77" t="n">
+        <v>2.0746</v>
+      </c>
+      <c r="G77" t="n">
         <v>232.6765</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>365.2175</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.8243</v>
       </c>
       <c r="F78" t="n">
+        <v>2.0846</v>
+      </c>
+      <c r="G78" t="n">
         <v>242.4358</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>366.9045</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.802</v>
       </c>
       <c r="F79" t="n">
+        <v>2.0824</v>
+      </c>
+      <c r="G79" t="n">
         <v>250.8977</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>366.5335</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.8004</v>
       </c>
       <c r="F80" t="n">
+        <v>2.0844</v>
+      </c>
+      <c r="G80" t="n">
         <v>250.9858</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>366.8683</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.8552</v>
       </c>
       <c r="F81" t="n">
+        <v>2.0106</v>
+      </c>
+      <c r="G81" t="n">
         <v>236.1438</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>354.1679</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.8542999999999999</v>
       </c>
       <c r="F82" t="n">
+        <v>2.0111</v>
+      </c>
+      <c r="G82" t="n">
         <v>235.1017</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>354.2557</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.9748</v>
       </c>
       <c r="F83" t="n">
+        <v>1.5291</v>
+      </c>
+      <c r="G83" t="n">
         <v>90.7975</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>256.2721</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.974</v>
       </c>
       <c r="F84" t="n">
+        <v>1.5244</v>
+      </c>
+      <c r="G84" t="n">
         <v>91.16540000000001</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>255.1345</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.975</v>
       </c>
       <c r="F85" t="n">
+        <v>1.5303</v>
+      </c>
+      <c r="G85" t="n">
         <v>90.8227</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>256.5464</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.9787</v>
       </c>
       <c r="F86" t="n">
+        <v>1.4858</v>
+      </c>
+      <c r="G86" t="n">
         <v>84.4542</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>245.5629</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.9788</v>
       </c>
       <c r="F87" t="n">
+        <v>1.4872</v>
+      </c>
+      <c r="G87" t="n">
         <v>86.7581</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>245.9053</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.967</v>
       </c>
       <c r="F88" t="n">
+        <v>1.4588</v>
+      </c>
+      <c r="G88" t="n">
         <v>100.7658</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>238.6303</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9665</v>
       </c>
       <c r="F89" t="n">
+        <v>1.4662</v>
+      </c>
+      <c r="G89" t="n">
         <v>101.7578</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>240.5505</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9866</v>
       </c>
       <c r="F90" t="n">
+        <v>1.4406</v>
+      </c>
+      <c r="G90" t="n">
         <v>76.1592</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>233.8439</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9858</v>
       </c>
       <c r="F91" t="n">
+        <v>1.4432</v>
+      </c>
+      <c r="G91" t="n">
         <v>72.6203</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>234.5405</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.967</v>
       </c>
       <c r="F92" t="n">
+        <v>1.4588</v>
+      </c>
+      <c r="G92" t="n">
         <v>100.7658</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>238.6303</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9858</v>
       </c>
       <c r="F93" t="n">
+        <v>1.4432</v>
+      </c>
+      <c r="G93" t="n">
         <v>72.6203</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>234.5405</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9775</v>
       </c>
       <c r="F94" t="n">
+        <v>1.5698</v>
+      </c>
+      <c r="G94" t="n">
         <v>94.026</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>265.9517</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.7496</v>
       </c>
       <c r="F95" t="n">
+        <v>2.1751</v>
+      </c>
+      <c r="G95" t="n">
         <v>264.5763</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>381.9164</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9789</v>
       </c>
       <c r="F96" t="n">
+        <v>1.5817</v>
+      </c>
+      <c r="G96" t="n">
         <v>91.86360000000001</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>268.7021</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="F97" t="n">
+        <v>1.582</v>
+      </c>
+      <c r="G97" t="n">
         <v>92.9584</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>268.7802</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9822</v>
       </c>
       <c r="F98" t="n">
+        <v>1.4552</v>
+      </c>
+      <c r="G98" t="n">
         <v>81.31399999999999</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>237.6991</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9626</v>
       </c>
       <c r="F99" t="n">
+        <v>1.4464</v>
+      </c>
+      <c r="G99" t="n">
         <v>107.9401</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>235.3773</v>
       </c>
     </row>
@@ -3318,9 +3617,12 @@
         <v>0.9801</v>
       </c>
       <c r="F100" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="G100" t="n">
         <v>83.2572</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>236.8634</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9595</v>
       </c>
       <c r="F101" t="n">
+        <v>1.455</v>
+      </c>
+      <c r="G101" t="n">
         <v>111.5956</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>237.6393</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9586</v>
       </c>
       <c r="F102" t="n">
+        <v>1.4652</v>
+      </c>
+      <c r="G102" t="n">
         <v>112.3118</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>240.2865</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="F103" t="n">
+        <v>1.4579</v>
+      </c>
+      <c r="G103" t="n">
         <v>81.9766</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>238.4081</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.9815</v>
       </c>
       <c r="F104" t="n">
+        <v>1.4579</v>
+      </c>
+      <c r="G104" t="n">
         <v>83.1315</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>238.4114</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9804</v>
       </c>
       <c r="F105" t="n">
+        <v>1.4516</v>
+      </c>
+      <c r="G105" t="n">
         <v>83.352</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>236.7661</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9636</v>
       </c>
       <c r="F106" t="n">
+        <v>1.4524</v>
+      </c>
+      <c r="G106" t="n">
         <v>106.9045</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>236.9577</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9604</v>
       </c>
       <c r="F107" t="n">
+        <v>1.4553</v>
+      </c>
+      <c r="G107" t="n">
         <v>110.0998</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>237.7197</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9825</v>
       </c>
       <c r="F108" t="n">
+        <v>1.4654</v>
+      </c>
+      <c r="G108" t="n">
         <v>83.64319999999999</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>240.3379</v>
       </c>
     </row>
@@ -3579,9 +3905,12 @@
         <v>0.9747</v>
       </c>
       <c r="F109" t="n">
+        <v>1.422</v>
+      </c>
+      <c r="G109" t="n">
         <v>90.88120000000001</v>
       </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>228.8701</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9823</v>
       </c>
       <c r="F110" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="G110" t="n">
         <v>80.6255</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>234.7608</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9817</v>
       </c>
       <c r="F111" t="n">
+        <v>1.4383</v>
+      </c>
+      <c r="G111" t="n">
         <v>81.04940000000001</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>233.2302</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9824000000000001</v>
       </c>
       <c r="F112" t="n">
+        <v>1.4655</v>
+      </c>
+      <c r="G112" t="n">
         <v>83.53700000000001</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>240.37</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9745</v>
       </c>
       <c r="F113" t="n">
+        <v>1.4211</v>
+      </c>
+      <c r="G113" t="n">
         <v>91.33159999999999</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>228.6304</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.977</v>
       </c>
       <c r="F114" t="n">
+        <v>1.4365</v>
+      </c>
+      <c r="G114" t="n">
         <v>85.42910000000001</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>232.7535</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9828</v>
       </c>
       <c r="F115" t="n">
+        <v>1.4311</v>
+      </c>
+      <c r="G115" t="n">
         <v>79.4413</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>231.3174</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.9304</v>
       </c>
       <c r="F116" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="G116" t="n">
         <v>180.5158</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>356.6879</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.8527</v>
       </c>
       <c r="F117" t="n">
+        <v>2.0134</v>
+      </c>
+      <c r="G117" t="n">
         <v>226.2557</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>354.6575</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9804</v>
       </c>
       <c r="F118" t="n">
+        <v>1.4516</v>
+      </c>
+      <c r="G118" t="n">
         <v>83.352</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>236.7661</v>
       </c>
     </row>
@@ -3869,9 +4225,12 @@
         <v>0.9745</v>
       </c>
       <c r="F119" t="n">
+        <v>1.4211</v>
+      </c>
+      <c r="G119" t="n">
         <v>91.33159999999999</v>
       </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>228.6304</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.8964</v>
       </c>
       <c r="F120" t="n">
+        <v>1.5176</v>
+      </c>
+      <c r="G120" t="n">
         <v>162.0505</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>253.4733</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.8964</v>
       </c>
       <c r="F121" t="n">
+        <v>1.5176</v>
+      </c>
+      <c r="G121" t="n">
         <v>162.0505</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>253.4733</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9366</v>
       </c>
       <c r="F122" t="n">
+        <v>1.4611</v>
+      </c>
+      <c r="G122" t="n">
         <v>134.4979</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>239.2284</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9823</v>
       </c>
       <c r="F123" t="n">
+        <v>1.4212</v>
+      </c>
+      <c r="G123" t="n">
         <v>78.7385</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>228.6513</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9816</v>
       </c>
       <c r="F124" t="n">
+        <v>1.4339</v>
+      </c>
+      <c r="G124" t="n">
         <v>80.99630000000001</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>232.0748</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9442</v>
       </c>
       <c r="F125" t="n">
+        <v>1.5909</v>
+      </c>
+      <c r="G125" t="n">
         <v>133.9448</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>270.8245</v>
       </c>
     </row>
@@ -4072,9 +4449,12 @@
         <v>0.9823</v>
       </c>
       <c r="F126" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G126" t="n">
         <v>83.3531</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>251.5898</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.8561</v>
       </c>
       <c r="F127" t="n">
+        <v>2.0637</v>
+      </c>
+      <c r="G127" t="n">
         <v>223.916</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>363.3514</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.9811</v>
       </c>
       <c r="F128" t="n">
+        <v>1.5095</v>
+      </c>
+      <c r="G128" t="n">
         <v>83.87</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>251.4823</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.9821</v>
       </c>
       <c r="F129" t="n">
+        <v>1.5206</v>
+      </c>
+      <c r="G129" t="n">
         <v>81.5492</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>254.2119</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.9808</v>
       </c>
       <c r="F130" t="n">
+        <v>1.5056</v>
+      </c>
+      <c r="G130" t="n">
         <v>85.2962</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>250.5</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.9809</v>
       </c>
       <c r="F131" t="n">
+        <v>1.5058</v>
+      </c>
+      <c r="G131" t="n">
         <v>84.0433</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>250.5492</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.9825</v>
       </c>
       <c r="F132" t="n">
+        <v>1.4984</v>
+      </c>
+      <c r="G132" t="n">
         <v>82.889</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>248.7274</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.9819</v>
       </c>
       <c r="F133" t="n">
+        <v>1.4976</v>
+      </c>
+      <c r="G133" t="n">
         <v>82.7163</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>248.52</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.9807</v>
       </c>
       <c r="F134" t="n">
+        <v>1.5025</v>
+      </c>
+      <c r="G134" t="n">
         <v>84.7068</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>249.7361</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.9815</v>
       </c>
       <c r="F135" t="n">
+        <v>1.5078</v>
+      </c>
+      <c r="G135" t="n">
         <v>83.97029999999999</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>251.0583</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.9816</v>
       </c>
       <c r="F136" t="n">
+        <v>1.5049</v>
+      </c>
+      <c r="G136" t="n">
         <v>83.5458</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>250.333</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9611</v>
       </c>
       <c r="F137" t="n">
+        <v>1.4675</v>
+      </c>
+      <c r="G137" t="n">
         <v>109.0518</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>240.8848</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9701</v>
       </c>
       <c r="F138" t="n">
+        <v>1.4745</v>
+      </c>
+      <c r="G138" t="n">
         <v>99.7942</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>242.6957</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9693000000000001</v>
       </c>
       <c r="F139" t="n">
+        <v>1.4717</v>
+      </c>
+      <c r="G139" t="n">
         <v>99.108</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>241.9638</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.9713000000000001</v>
       </c>
       <c r="F140" t="n">
+        <v>1.4084</v>
+      </c>
+      <c r="G140" t="n">
         <v>91.4914</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>225.1426</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9801</v>
       </c>
       <c r="F141" t="n">
+        <v>1.4345</v>
+      </c>
+      <c r="G141" t="n">
         <v>82.8646</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>232.2176</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9701</v>
       </c>
       <c r="F142" t="n">
+        <v>1.4745</v>
+      </c>
+      <c r="G142" t="n">
         <v>99.7942</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>242.6957</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9706</v>
       </c>
       <c r="F143" t="n">
+        <v>1.4415</v>
+      </c>
+      <c r="G143" t="n">
         <v>95.77119999999999</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>234.0818</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9713000000000001</v>
       </c>
       <c r="F144" t="n">
+        <v>1.4611</v>
+      </c>
+      <c r="G144" t="n">
         <v>96.3704</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>239.2396</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9801</v>
       </c>
       <c r="F145" t="n">
+        <v>1.4345</v>
+      </c>
+      <c r="G145" t="n">
         <v>82.8646</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>232.2176</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.8397</v>
       </c>
       <c r="F146" t="n">
+        <v>2.0536</v>
+      </c>
+      <c r="G146" t="n">
         <v>232.145</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>361.626</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.8375</v>
       </c>
       <c r="F147" t="n">
+        <v>2.0546</v>
+      </c>
+      <c r="G147" t="n">
         <v>232.6473</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>361.7929</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.8362000000000001</v>
       </c>
       <c r="F148" t="n">
+        <v>2.0519</v>
+      </c>
+      <c r="G148" t="n">
         <v>232.3384</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>361.3305</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.8649</v>
       </c>
       <c r="F149" t="n">
+        <v>2.0488</v>
+      </c>
+      <c r="G149" t="n">
         <v>221.077</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>360.8039</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.836</v>
       </c>
       <c r="F150" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="G150" t="n">
         <v>231.8782</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>363.0733</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.8386</v>
       </c>
       <c r="F151" t="n">
+        <v>2.0544</v>
+      </c>
+      <c r="G151" t="n">
         <v>230.8075</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>361.7634</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.8406</v>
       </c>
       <c r="F152" t="n">
+        <v>2.0526</v>
+      </c>
+      <c r="G152" t="n">
         <v>230.8476</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>361.4492</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.8362000000000001</v>
       </c>
       <c r="F153" t="n">
+        <v>2.0592</v>
+      </c>
+      <c r="G153" t="n">
         <v>232.9255</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>362.5899</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.8344</v>
       </c>
       <c r="F154" t="n">
+        <v>2.0497</v>
+      </c>
+      <c r="G154" t="n">
         <v>231.8489</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>360.9492</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.8764</v>
       </c>
       <c r="F155" t="n">
+        <v>2.0398</v>
+      </c>
+      <c r="G155" t="n">
         <v>228.2008</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>359.2558</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.8505</v>
       </c>
       <c r="F156" t="n">
+        <v>2.0454</v>
+      </c>
+      <c r="G156" t="n">
         <v>238.8687</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>360.2218</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.8759</v>
       </c>
       <c r="F157" t="n">
+        <v>2.0393</v>
+      </c>
+      <c r="G157" t="n">
         <v>227.3839</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>359.1725</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.8742</v>
       </c>
       <c r="F158" t="n">
+        <v>1.9697</v>
+      </c>
+      <c r="G158" t="n">
         <v>230.0989</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>346.9333</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.9772999999999999</v>
       </c>
       <c r="F159" t="n">
+        <v>1.4659</v>
+      </c>
+      <c r="G159" t="n">
         <v>84.96429999999999</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>240.4694</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.8462</v>
       </c>
       <c r="F160" t="n">
+        <v>2.0585</v>
+      </c>
+      <c r="G160" t="n">
         <v>242.6177</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>362.46</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.8581</v>
       </c>
       <c r="F161" t="n">
+        <v>2.0528</v>
+      </c>
+      <c r="G161" t="n">
         <v>231.0193</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>361.4839</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.9609</v>
       </c>
       <c r="F162" t="n">
+        <v>1.4778</v>
+      </c>
+      <c r="G162" t="n">
         <v>109.176</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>243.5304</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9712</v>
       </c>
       <c r="F163" t="n">
+        <v>1.4958</v>
+      </c>
+      <c r="G163" t="n">
         <v>96.669</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>248.084</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.9712</v>
       </c>
       <c r="F164" t="n">
+        <v>1.4075</v>
+      </c>
+      <c r="G164" t="n">
         <v>91.63760000000001</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>224.8966</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9442</v>
       </c>
       <c r="F165" t="n">
+        <v>1.5909</v>
+      </c>
+      <c r="G165" t="n">
         <v>133.9448</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>270.8245</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.7458</v>
       </c>
       <c r="F166" t="n">
+        <v>2.1736</v>
+      </c>
+      <c r="G166" t="n">
         <v>265.7293</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>381.6626</v>
       </c>
     </row>
@@ -5261,9 +5761,12 @@
         <v>0.9722</v>
       </c>
       <c r="F167" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G167" t="n">
         <v>92.24890000000001</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>222.8232</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9791</v>
       </c>
       <c r="F168" t="n">
+        <v>1.3845</v>
+      </c>
+      <c r="G168" t="n">
         <v>77.5085</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>218.4699</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9534</v>
       </c>
       <c r="F169" t="n">
+        <v>1.4908</v>
+      </c>
+      <c r="G169" t="n">
         <v>122.3717</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>246.8227</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9804</v>
       </c>
       <c r="F170" t="n">
+        <v>1.4574</v>
+      </c>
+      <c r="G170" t="n">
         <v>82.3142</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>238.2644</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9839</v>
       </c>
       <c r="F171" t="n">
+        <v>1.4223</v>
+      </c>
+      <c r="G171" t="n">
         <v>76.9773</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>228.941</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9683</v>
       </c>
       <c r="F172" t="n">
+        <v>1.4577</v>
+      </c>
+      <c r="G172" t="n">
         <v>98.7353</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>238.3591</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
@@ -474,20 +474,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9796</v>
+        <v>0.9231</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4754</v>
+        <v>0.4928</v>
       </c>
       <c r="G2" t="n">
-        <v>86.7587</v>
+        <v>148.5175</v>
       </c>
       <c r="H2" t="n">
-        <v>242.922</v>
+        <v>250.8646</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9711</v>
+        <v>0.9459</v>
       </c>
       <c r="F3" t="n">
-        <v>1.477</v>
+        <v>0.5481</v>
       </c>
       <c r="G3" t="n">
-        <v>101.0696</v>
+        <v>124.9566</v>
       </c>
       <c r="H3" t="n">
-        <v>243.3102</v>
+        <v>236.781</v>
       </c>
     </row>
     <row r="4">
@@ -538,20 +538,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9775</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5698</v>
+        <v>0.4422</v>
       </c>
       <c r="G4" t="n">
-        <v>94.026</v>
+        <v>169.9043</v>
       </c>
       <c r="H4" t="n">
-        <v>265.9517</v>
+        <v>263.0619</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8739</v>
+        <v>0.8666</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0638</v>
+        <v>-0.1087</v>
       </c>
       <c r="G5" t="n">
-        <v>218.5961</v>
+        <v>236.0076</v>
       </c>
       <c r="H5" t="n">
-        <v>363.3764</v>
+        <v>370.8825</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8438</v>
+        <v>0.8501</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0616</v>
+        <v>-0.0822</v>
       </c>
       <c r="G6" t="n">
-        <v>232.3914</v>
+        <v>240.1509</v>
       </c>
       <c r="H6" t="n">
-        <v>363.0053</v>
+        <v>366.4286</v>
       </c>
     </row>
     <row r="7">
@@ -634,20 +634,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9727</v>
+        <v>0.9715</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5573</v>
+        <v>0.3759</v>
       </c>
       <c r="G7" t="n">
-        <v>94.9148</v>
+        <v>102.1284</v>
       </c>
       <c r="H7" t="n">
-        <v>263.0181</v>
+        <v>278.2712</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.979</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1.496</v>
+        <v>0.4821</v>
       </c>
       <c r="G8" t="n">
-        <v>83.9616</v>
+        <v>98.2959</v>
       </c>
       <c r="H8" t="n">
-        <v>248.1219</v>
+        <v>253.4927</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9843</v>
+        <v>0.9802</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4397</v>
+        <v>0.5796</v>
       </c>
       <c r="G9" t="n">
-        <v>73.8614</v>
+        <v>85.5125</v>
       </c>
       <c r="H9" t="n">
-        <v>233.6199</v>
+        <v>228.3751</v>
       </c>
     </row>
     <row r="10">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9777</v>
+        <v>0.9739</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4906</v>
+        <v>0.4862</v>
       </c>
       <c r="G10" t="n">
-        <v>85.3206</v>
+        <v>97.71639999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>246.7607</v>
+        <v>252.475</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9706</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4867</v>
+        <v>0.495</v>
       </c>
       <c r="G11" t="n">
-        <v>97.871</v>
+        <v>95.676</v>
       </c>
       <c r="H11" t="n">
-        <v>245.7767</v>
+        <v>250.2989</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9777</v>
+        <v>0.9721</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4871</v>
+        <v>0.4937</v>
       </c>
       <c r="G12" t="n">
-        <v>84.45440000000001</v>
+        <v>95.91849999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>245.8881</v>
+        <v>250.6288</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9606</v>
+        <v>0.9739</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4893</v>
+        <v>0.4908</v>
       </c>
       <c r="G13" t="n">
-        <v>110.8643</v>
+        <v>94.46120000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>246.4312</v>
+        <v>251.3403</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9706</v>
+        <v>0.9741</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4908</v>
+        <v>0.49</v>
       </c>
       <c r="G14" t="n">
-        <v>98.3146</v>
+        <v>95.9662</v>
       </c>
       <c r="H14" t="n">
-        <v>246.8296</v>
+        <v>251.5348</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9791</v>
+        <v>0.9731</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4842</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>82.43680000000001</v>
+        <v>94.49679999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>245.1536</v>
+        <v>248.6933</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9795</v>
+        <v>0.9732</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4836</v>
+        <v>0.5117</v>
       </c>
       <c r="G16" t="n">
-        <v>81.6502</v>
+        <v>96.6614</v>
       </c>
       <c r="H16" t="n">
-        <v>244.9911</v>
+        <v>246.1232</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9711</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4818</v>
+        <v>0.5067</v>
       </c>
       <c r="G17" t="n">
-        <v>96.6914</v>
+        <v>96.6037</v>
       </c>
       <c r="H17" t="n">
-        <v>244.5361</v>
+        <v>247.3868</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4676</v>
+        <v>0.484</v>
       </c>
       <c r="G18" t="n">
-        <v>109.9168</v>
+        <v>139.5779</v>
       </c>
       <c r="H18" t="n">
-        <v>240.9008</v>
+        <v>253.0097</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9787</v>
+        <v>0.9391</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4487</v>
+        <v>0.5088</v>
       </c>
       <c r="G19" t="n">
-        <v>83.5843</v>
+        <v>131.2587</v>
       </c>
       <c r="H19" t="n">
-        <v>235.9899</v>
+        <v>246.8691</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9343</v>
       </c>
       <c r="F20" t="n">
-        <v>1.454</v>
+        <v>0.5061</v>
       </c>
       <c r="G20" t="n">
-        <v>99.3426</v>
+        <v>135.7672</v>
       </c>
       <c r="H20" t="n">
-        <v>237.3937</v>
+        <v>247.5446</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9453</v>
+        <v>0.9688</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4367</v>
+        <v>0.5182</v>
       </c>
       <c r="G21" t="n">
-        <v>124.7277</v>
+        <v>99.0673</v>
       </c>
       <c r="H21" t="n">
-        <v>232.8284</v>
+        <v>244.48</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9645</v>
+        <v>0.9771</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4669</v>
+        <v>0.4961</v>
       </c>
       <c r="G22" t="n">
-        <v>101.7267</v>
+        <v>89.18510000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>240.742</v>
+        <v>250.0324</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9573</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4739</v>
+        <v>0.4923</v>
       </c>
       <c r="G23" t="n">
-        <v>112.6289</v>
+        <v>90.6859</v>
       </c>
       <c r="H23" t="n">
-        <v>242.5427</v>
+        <v>250.9826</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9588</v>
+        <v>0.977</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4781</v>
+        <v>0.4974</v>
       </c>
       <c r="G24" t="n">
-        <v>112.4172</v>
+        <v>91.5789</v>
       </c>
       <c r="H24" t="n">
-        <v>243.615</v>
+        <v>249.7116</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9616</v>
+        <v>0.9767</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4735</v>
+        <v>0.4974</v>
       </c>
       <c r="G25" t="n">
-        <v>106.5943</v>
+        <v>89.56359999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>242.4349</v>
+        <v>249.7097</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.981</v>
+        <v>0.9324</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4867</v>
+        <v>0.4875</v>
       </c>
       <c r="G26" t="n">
-        <v>83.94840000000001</v>
+        <v>136.4416</v>
       </c>
       <c r="H26" t="n">
-        <v>245.7808</v>
+        <v>252.1543</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9772</v>
+        <v>0.9287</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4703</v>
+        <v>0.4797</v>
       </c>
       <c r="G27" t="n">
-        <v>88.2679</v>
+        <v>140.5045</v>
       </c>
       <c r="H27" t="n">
-        <v>241.6203</v>
+        <v>254.0682</v>
       </c>
     </row>
     <row r="28">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9774</v>
+        <v>0.9578</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4473</v>
+        <v>0.5049</v>
       </c>
       <c r="G28" t="n">
-        <v>85.38630000000001</v>
+        <v>112.3844</v>
       </c>
       <c r="H28" t="n">
-        <v>235.6195</v>
+        <v>247.849</v>
       </c>
     </row>
     <row r="29">
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9687</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4516</v>
+        <v>0.5124</v>
       </c>
       <c r="G29" t="n">
-        <v>97.7431</v>
+        <v>109.9166</v>
       </c>
       <c r="H29" t="n">
-        <v>236.7572</v>
+        <v>245.9522</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9679</v>
+        <v>0.9336</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4507</v>
+        <v>0.4984</v>
       </c>
       <c r="G30" t="n">
-        <v>99.9156</v>
+        <v>135.0356</v>
       </c>
       <c r="H30" t="n">
-        <v>236.5194</v>
+        <v>249.4665</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9379</v>
+        <v>0.9655</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4441</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>129.9549</v>
+        <v>103.843</v>
       </c>
       <c r="H31" t="n">
-        <v>234.7886</v>
+        <v>248.9441</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9768</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4346</v>
+        <v>0.5022</v>
       </c>
       <c r="G32" t="n">
-        <v>81.84050000000001</v>
+        <v>89.3916</v>
       </c>
       <c r="H32" t="n">
-        <v>232.2462</v>
+        <v>248.528</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.981</v>
+        <v>0.9676</v>
       </c>
       <c r="F33" t="n">
-        <v>1.4492</v>
+        <v>0.5004</v>
       </c>
       <c r="G33" t="n">
-        <v>79.1925</v>
+        <v>102.9034</v>
       </c>
       <c r="H33" t="n">
-        <v>236.138</v>
+        <v>248.9568</v>
       </c>
     </row>
     <row r="34">
@@ -1498,20 +1498,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9789</v>
+        <v>0.9749</v>
       </c>
       <c r="F34" t="n">
-        <v>1.4095</v>
+        <v>0.582</v>
       </c>
       <c r="G34" t="n">
-        <v>85.002</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>225.4402</v>
+        <v>227.7322</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9573</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3946</v>
+        <v>0.59</v>
       </c>
       <c r="G35" t="n">
-        <v>85.3811</v>
+        <v>114.8146</v>
       </c>
       <c r="H35" t="n">
-        <v>221.3179</v>
+        <v>225.5368</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9868</v>
+        <v>0.9505</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4255</v>
+        <v>0.5802</v>
       </c>
       <c r="G36" t="n">
-        <v>74.94370000000001</v>
+        <v>120.2751</v>
       </c>
       <c r="H36" t="n">
-        <v>229.803</v>
+        <v>228.2188</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.984</v>
+        <v>0.9698</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4384</v>
+        <v>0.5759</v>
       </c>
       <c r="G37" t="n">
-        <v>74.2026</v>
+        <v>99.22929999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>233.2675</v>
+        <v>229.3938</v>
       </c>
     </row>
     <row r="38">
@@ -1626,20 +1626,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9862</v>
+        <v>0.9826</v>
       </c>
       <c r="F38" t="n">
-        <v>1.4208</v>
+        <v>0.5849</v>
       </c>
       <c r="G38" t="n">
-        <v>71.9222</v>
+        <v>80.4042</v>
       </c>
       <c r="H38" t="n">
-        <v>228.5267</v>
+        <v>226.9455</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9707</v>
+        <v>0.9771</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4513</v>
+        <v>0.5561</v>
       </c>
       <c r="G39" t="n">
-        <v>99.6294</v>
+        <v>87.553</v>
       </c>
       <c r="H39" t="n">
-        <v>236.679</v>
+        <v>234.6737</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.97</v>
+        <v>0.9358</v>
       </c>
       <c r="F40" t="n">
-        <v>1.4649</v>
+        <v>0.5346</v>
       </c>
       <c r="G40" t="n">
-        <v>100.6551</v>
+        <v>137.2032</v>
       </c>
       <c r="H40" t="n">
-        <v>240.2132</v>
+        <v>240.2949</v>
       </c>
     </row>
     <row r="41">
@@ -1722,20 +1722,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9787</v>
+        <v>0.9749</v>
       </c>
       <c r="F41" t="n">
-        <v>1.4114</v>
+        <v>0.5839</v>
       </c>
       <c r="G41" t="n">
-        <v>85.07940000000001</v>
+        <v>92.4866</v>
       </c>
       <c r="H41" t="n">
-        <v>225.965</v>
+        <v>227.2004</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9771</v>
+        <v>0.9573</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3957</v>
+        <v>0.5887</v>
       </c>
       <c r="G42" t="n">
-        <v>87.5274</v>
+        <v>114.8064</v>
       </c>
       <c r="H42" t="n">
-        <v>221.6226</v>
+        <v>225.8918</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9866</v>
+        <v>0.9504</v>
       </c>
       <c r="F43" t="n">
-        <v>1.4401</v>
+        <v>0.5793</v>
       </c>
       <c r="G43" t="n">
-        <v>76.1677</v>
+        <v>120.4662</v>
       </c>
       <c r="H43" t="n">
-        <v>233.718</v>
+        <v>228.4676</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9858</v>
+        <v>0.9819</v>
       </c>
       <c r="F44" t="n">
-        <v>1.4426</v>
+        <v>0.578</v>
       </c>
       <c r="G44" t="n">
-        <v>72.6203</v>
+        <v>82.4598</v>
       </c>
       <c r="H44" t="n">
-        <v>234.3743</v>
+        <v>228.8126</v>
       </c>
     </row>
     <row r="45">
@@ -1850,20 +1850,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9853</v>
+        <v>0.9794</v>
       </c>
       <c r="F45" t="n">
-        <v>1.4297</v>
+        <v>0.5742</v>
       </c>
       <c r="G45" t="n">
-        <v>74.0673</v>
+        <v>85.7666</v>
       </c>
       <c r="H45" t="n">
-        <v>230.9389</v>
+        <v>229.8555</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9702</v>
+        <v>0.9371</v>
       </c>
       <c r="F46" t="n">
-        <v>1.468</v>
+        <v>0.5565</v>
       </c>
       <c r="G46" t="n">
-        <v>101.3525</v>
+        <v>135.051</v>
       </c>
       <c r="H46" t="n">
-        <v>241.0197</v>
+        <v>234.5765</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.971</v>
+        <v>0.9373</v>
       </c>
       <c r="F47" t="n">
-        <v>1.4607</v>
+        <v>0.5675</v>
       </c>
       <c r="G47" t="n">
-        <v>100.1909</v>
+        <v>135.5069</v>
       </c>
       <c r="H47" t="n">
-        <v>239.1284</v>
+        <v>231.6525</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9855</v>
+        <v>0.9667</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4396</v>
+        <v>0.5898</v>
       </c>
       <c r="G48" t="n">
-        <v>78.039</v>
+        <v>105.0492</v>
       </c>
       <c r="H48" t="n">
-        <v>233.5794</v>
+        <v>225.5953</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9738</v>
+        <v>0.9456</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4356</v>
+        <v>0.584</v>
       </c>
       <c r="G49" t="n">
-        <v>95.00490000000001</v>
+        <v>124.4223</v>
       </c>
       <c r="H49" t="n">
-        <v>232.5281</v>
+        <v>227.1768</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9152</v>
+        <v>0.9137</v>
       </c>
       <c r="F50" t="n">
-        <v>1.9789</v>
+        <v>0.0073</v>
       </c>
       <c r="G50" t="n">
-        <v>205.4592</v>
+        <v>221.536</v>
       </c>
       <c r="H50" t="n">
-        <v>348.5644</v>
+        <v>350.9549</v>
       </c>
     </row>
     <row r="51">
@@ -2042,20 +2042,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8498</v>
+        <v>0.9452</v>
       </c>
       <c r="F51" t="n">
-        <v>1.9867</v>
+        <v>0.0559</v>
       </c>
       <c r="G51" t="n">
-        <v>237.0721</v>
+        <v>175.9396</v>
       </c>
       <c r="H51" t="n">
-        <v>349.958</v>
+        <v>342.2413</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8753</v>
+        <v>0.8851</v>
       </c>
       <c r="F52" t="n">
-        <v>1.9897</v>
+        <v>0.0347</v>
       </c>
       <c r="G52" t="n">
-        <v>218.7054</v>
+        <v>226.9934</v>
       </c>
       <c r="H52" t="n">
-        <v>350.4963</v>
+        <v>346.0616</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9076</v>
+        <v>0.9637</v>
       </c>
       <c r="F53" t="n">
-        <v>1.8969</v>
+        <v>0.1374</v>
       </c>
       <c r="G53" t="n">
-        <v>206.9783</v>
+        <v>156.7735</v>
       </c>
       <c r="H53" t="n">
-        <v>333.6465</v>
+        <v>327.1416</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8977000000000001</v>
+        <v>0.917</v>
       </c>
       <c r="F54" t="n">
-        <v>1.8635</v>
+        <v>0.1908</v>
       </c>
       <c r="G54" t="n">
-        <v>207.1178</v>
+        <v>193.2808</v>
       </c>
       <c r="H54" t="n">
-        <v>327.3914</v>
+        <v>316.8466</v>
       </c>
     </row>
     <row r="55">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8699</v>
+        <v>0.9081</v>
       </c>
       <c r="F55" t="n">
-        <v>2.0006</v>
+        <v>-0.0286</v>
       </c>
       <c r="G55" t="n">
-        <v>232.6325</v>
+        <v>227.439</v>
       </c>
       <c r="H55" t="n">
-        <v>352.4195</v>
+        <v>357.2365</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.9196</v>
       </c>
       <c r="F56" t="n">
-        <v>1.9965</v>
+        <v>-0.0157</v>
       </c>
       <c r="G56" t="n">
-        <v>231.1333</v>
+        <v>225.8088</v>
       </c>
       <c r="H56" t="n">
-        <v>351.6996</v>
+        <v>354.9834</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9494</v>
+        <v>0.9042</v>
       </c>
       <c r="F57" t="n">
-        <v>1.9818</v>
+        <v>-0.0112</v>
       </c>
       <c r="G57" t="n">
-        <v>166.213</v>
+        <v>225.81</v>
       </c>
       <c r="H57" t="n">
-        <v>349.096</v>
+        <v>354.2083</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8471</v>
+        <v>0.8476</v>
       </c>
       <c r="F58" t="n">
-        <v>2.0667</v>
+        <v>-0.0819</v>
       </c>
       <c r="G58" t="n">
-        <v>231.5552</v>
+        <v>241.7978</v>
       </c>
       <c r="H58" t="n">
-        <v>363.8753</v>
+        <v>366.3692</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.8424</v>
+        <v>0.8465</v>
       </c>
       <c r="F59" t="n">
-        <v>2.0629</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>233.443</v>
+        <v>241.9658</v>
       </c>
       <c r="H59" t="n">
-        <v>363.2236</v>
+        <v>368.2765</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.8364</v>
+        <v>0.847</v>
       </c>
       <c r="F60" t="n">
-        <v>2.0572</v>
+        <v>-0.0882</v>
       </c>
       <c r="G60" t="n">
-        <v>233.6898</v>
+        <v>242.1576</v>
       </c>
       <c r="H60" t="n">
-        <v>362.2392</v>
+        <v>367.4475</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.8306</v>
+        <v>0.8484</v>
       </c>
       <c r="F61" t="n">
-        <v>2.058</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>235.3027</v>
+        <v>241.1527</v>
       </c>
       <c r="H61" t="n">
-        <v>362.3811</v>
+        <v>367.7335</v>
       </c>
     </row>
     <row r="62">
@@ -2398,16 +2398,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8685</v>
+        <v>0.8919</v>
       </c>
       <c r="F62" t="n">
-        <v>2.0419</v>
+        <v>-0.0183</v>
       </c>
       <c r="G62" t="n">
-        <v>228.4433</v>
+        <v>232.1394</v>
       </c>
       <c r="H62" t="n">
-        <v>359.6111</v>
+        <v>355.4376</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8436</v>
+        <v>0.9069</v>
       </c>
       <c r="F63" t="n">
-        <v>2.0384</v>
+        <v>-0.0239</v>
       </c>
       <c r="G63" t="n">
-        <v>239.271</v>
+        <v>218.9878</v>
       </c>
       <c r="H63" t="n">
-        <v>359.0133</v>
+        <v>356.4239</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.845</v>
+        <v>0.8837</v>
       </c>
       <c r="F64" t="n">
-        <v>2.0399</v>
+        <v>-0.0281</v>
       </c>
       <c r="G64" t="n">
-        <v>239.2279</v>
+        <v>232.2232</v>
       </c>
       <c r="H64" t="n">
-        <v>359.2642</v>
+        <v>357.1458</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.839</v>
+        <v>0.8822</v>
       </c>
       <c r="F65" t="n">
-        <v>2.0339</v>
+        <v>-0.0338</v>
       </c>
       <c r="G65" t="n">
-        <v>240.0046</v>
+        <v>231.6588</v>
       </c>
       <c r="H65" t="n">
-        <v>358.2305</v>
+        <v>358.1323</v>
       </c>
     </row>
     <row r="66">
@@ -2526,16 +2526,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8925</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>1.9914</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>221.0742</v>
+        <v>222.6711</v>
       </c>
       <c r="H66" t="n">
-        <v>350.796</v>
+        <v>350.8426</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>1.9869</v>
+        <v>0.0028</v>
       </c>
       <c r="G67" t="n">
-        <v>232.5881</v>
+        <v>223.8539</v>
       </c>
       <c r="H67" t="n">
-        <v>349.9968</v>
+        <v>351.7391</v>
       </c>
     </row>
     <row r="68">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8673</v>
+        <v>0.8932</v>
       </c>
       <c r="F68" t="n">
-        <v>1.9985</v>
+        <v>0.0067</v>
       </c>
       <c r="G68" t="n">
-        <v>233.4053</v>
+        <v>236.3715</v>
       </c>
       <c r="H68" t="n">
-        <v>352.0432</v>
+        <v>351.0446</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.982</v>
+        <v>0.955</v>
       </c>
       <c r="F69" t="n">
-        <v>1.4513</v>
+        <v>0.5036</v>
       </c>
       <c r="G69" t="n">
-        <v>81.91079999999999</v>
+        <v>116.4844</v>
       </c>
       <c r="H69" t="n">
-        <v>236.6896</v>
+        <v>248.1769</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9804</v>
+        <v>0.9776</v>
       </c>
       <c r="F70" t="n">
-        <v>1.4613</v>
+        <v>0.4896</v>
       </c>
       <c r="G70" t="n">
-        <v>82.642</v>
+        <v>90.0544</v>
       </c>
       <c r="H70" t="n">
-        <v>239.2909</v>
+        <v>251.6349</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9797</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>1.4533</v>
+        <v>0.4964</v>
       </c>
       <c r="G71" t="n">
-        <v>84.39830000000001</v>
+        <v>90.9285</v>
       </c>
       <c r="H71" t="n">
-        <v>237.2127</v>
+        <v>249.9599</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9786</v>
+        <v>0.9555</v>
       </c>
       <c r="F72" t="n">
-        <v>1.4542</v>
+        <v>0.4964</v>
       </c>
       <c r="G72" t="n">
-        <v>85.8901</v>
+        <v>118.8174</v>
       </c>
       <c r="H72" t="n">
-        <v>237.4455</v>
+        <v>249.9534</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.983</v>
+        <v>0.9331</v>
       </c>
       <c r="F73" t="n">
-        <v>1.4442</v>
+        <v>0.5183</v>
       </c>
       <c r="G73" t="n">
-        <v>77.65940000000001</v>
+        <v>141.6004</v>
       </c>
       <c r="H73" t="n">
-        <v>234.7998</v>
+        <v>244.4776</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9729</v>
+        <v>0.9611</v>
       </c>
       <c r="F74" t="n">
-        <v>1.4425</v>
+        <v>0.5188</v>
       </c>
       <c r="G74" t="n">
-        <v>91.9653</v>
+        <v>110.4865</v>
       </c>
       <c r="H74" t="n">
-        <v>234.3634</v>
+        <v>244.3471</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9755</v>
+        <v>0.9737</v>
       </c>
       <c r="F75" t="n">
-        <v>1.5295</v>
+        <v>0.4091</v>
       </c>
       <c r="G75" t="n">
-        <v>90.1386</v>
+        <v>99.13079999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>256.3623</v>
+        <v>270.7553</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9755</v>
+        <v>0.9737</v>
       </c>
       <c r="F76" t="n">
-        <v>1.5295</v>
+        <v>0.4091</v>
       </c>
       <c r="G76" t="n">
-        <v>90.1386</v>
+        <v>99.13079999999999</v>
       </c>
       <c r="H76" t="n">
-        <v>256.3623</v>
+        <v>270.7553</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.844</v>
+        <v>0.8411</v>
       </c>
       <c r="F77" t="n">
-        <v>2.0746</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>232.6765</v>
+        <v>242.238</v>
       </c>
       <c r="H77" t="n">
-        <v>365.2175</v>
+        <v>368.8748</v>
       </c>
     </row>
     <row r="78">
@@ -2910,16 +2910,16 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8243</v>
+        <v>0.8318</v>
       </c>
       <c r="F78" t="n">
-        <v>2.0846</v>
+        <v>-0.0949</v>
       </c>
       <c r="G78" t="n">
-        <v>242.4358</v>
+        <v>250.2034</v>
       </c>
       <c r="H78" t="n">
-        <v>366.9045</v>
+        <v>368.5687</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.802</v>
+        <v>0.8324</v>
       </c>
       <c r="F79" t="n">
-        <v>2.0824</v>
+        <v>-0.0951</v>
       </c>
       <c r="G79" t="n">
-        <v>250.8977</v>
+        <v>250.3874</v>
       </c>
       <c r="H79" t="n">
-        <v>366.5335</v>
+        <v>368.5973</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8004</v>
+        <v>0.833</v>
       </c>
       <c r="F80" t="n">
-        <v>2.0844</v>
+        <v>-0.0944</v>
       </c>
       <c r="G80" t="n">
-        <v>250.9858</v>
+        <v>249.8753</v>
       </c>
       <c r="H80" t="n">
-        <v>366.8683</v>
+        <v>368.486</v>
       </c>
     </row>
     <row r="81">
@@ -3002,20 +3002,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8552</v>
+        <v>0.8965</v>
       </c>
       <c r="F81" t="n">
-        <v>2.0106</v>
+        <v>-0.0047</v>
       </c>
       <c r="G81" t="n">
-        <v>236.1438</v>
+        <v>229.1646</v>
       </c>
       <c r="H81" t="n">
-        <v>354.1679</v>
+        <v>353.054</v>
       </c>
     </row>
     <row r="82">
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.8703</v>
       </c>
       <c r="F82" t="n">
-        <v>2.0111</v>
+        <v>-0.0233</v>
       </c>
       <c r="G82" t="n">
-        <v>235.1017</v>
+        <v>241.6051</v>
       </c>
       <c r="H82" t="n">
-        <v>354.2557</v>
+        <v>356.3205</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9748</v>
+        <v>0.9734</v>
       </c>
       <c r="F83" t="n">
-        <v>1.5291</v>
+        <v>0.4072</v>
       </c>
       <c r="G83" t="n">
-        <v>90.7975</v>
+        <v>99.5119</v>
       </c>
       <c r="H83" t="n">
-        <v>256.2721</v>
+        <v>271.1966</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.974</v>
+        <v>0.9731</v>
       </c>
       <c r="F84" t="n">
-        <v>1.5244</v>
+        <v>0.4065</v>
       </c>
       <c r="G84" t="n">
-        <v>91.16540000000001</v>
+        <v>99.5188</v>
       </c>
       <c r="H84" t="n">
-        <v>255.1345</v>
+        <v>271.3539</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.975</v>
+        <v>0.9736</v>
       </c>
       <c r="F85" t="n">
-        <v>1.5303</v>
+        <v>0.4081</v>
       </c>
       <c r="G85" t="n">
-        <v>90.8227</v>
+        <v>99.2221</v>
       </c>
       <c r="H85" t="n">
-        <v>256.5464</v>
+        <v>270.9977</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9787</v>
+        <v>0.9305</v>
       </c>
       <c r="F86" t="n">
-        <v>1.4858</v>
+        <v>0.4811</v>
       </c>
       <c r="G86" t="n">
-        <v>84.4542</v>
+        <v>139.0515</v>
       </c>
       <c r="H86" t="n">
-        <v>245.5629</v>
+        <v>253.7259</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9788</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F87" t="n">
-        <v>1.4872</v>
+        <v>0.4943</v>
       </c>
       <c r="G87" t="n">
-        <v>86.7581</v>
+        <v>100.2966</v>
       </c>
       <c r="H87" t="n">
-        <v>245.9053</v>
+        <v>250.4814</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.967</v>
+        <v>0.9327</v>
       </c>
       <c r="F88" t="n">
-        <v>1.4588</v>
+        <v>0.4816</v>
       </c>
       <c r="G88" t="n">
-        <v>100.7658</v>
+        <v>137.9754</v>
       </c>
       <c r="H88" t="n">
-        <v>238.6303</v>
+        <v>253.6069</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9665</v>
+        <v>0.9297</v>
       </c>
       <c r="F89" t="n">
-        <v>1.4662</v>
+        <v>0.4916</v>
       </c>
       <c r="G89" t="n">
-        <v>101.7578</v>
+        <v>140.4245</v>
       </c>
       <c r="H89" t="n">
-        <v>240.5505</v>
+        <v>251.1568</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9866</v>
+        <v>0.9504</v>
       </c>
       <c r="F90" t="n">
-        <v>1.4406</v>
+        <v>0.5793</v>
       </c>
       <c r="G90" t="n">
-        <v>76.1592</v>
+        <v>120.4705</v>
       </c>
       <c r="H90" t="n">
-        <v>233.8439</v>
+        <v>228.4606</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9858</v>
+        <v>0.9818</v>
       </c>
       <c r="F91" t="n">
-        <v>1.4432</v>
+        <v>0.578</v>
       </c>
       <c r="G91" t="n">
-        <v>72.6203</v>
+        <v>82.5438</v>
       </c>
       <c r="H91" t="n">
-        <v>234.5405</v>
+        <v>228.8183</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.967</v>
+        <v>0.9327</v>
       </c>
       <c r="F92" t="n">
-        <v>1.4588</v>
+        <v>0.4816</v>
       </c>
       <c r="G92" t="n">
-        <v>100.7658</v>
+        <v>137.9754</v>
       </c>
       <c r="H92" t="n">
-        <v>238.6303</v>
+        <v>253.6069</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9858</v>
+        <v>0.9818</v>
       </c>
       <c r="F93" t="n">
-        <v>1.4432</v>
+        <v>0.578</v>
       </c>
       <c r="G93" t="n">
-        <v>72.6203</v>
+        <v>82.5438</v>
       </c>
       <c r="H93" t="n">
-        <v>234.5405</v>
+        <v>228.8183</v>
       </c>
     </row>
     <row r="94">
@@ -3418,20 +3418,20 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9775</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="F94" t="n">
-        <v>1.5698</v>
+        <v>0.4422</v>
       </c>
       <c r="G94" t="n">
-        <v>94.026</v>
+        <v>169.9043</v>
       </c>
       <c r="H94" t="n">
-        <v>265.9517</v>
+        <v>263.0619</v>
       </c>
     </row>
     <row r="95">
@@ -3454,16 +3454,16 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7496</v>
+        <v>0.6979</v>
       </c>
       <c r="F95" t="n">
-        <v>2.1751</v>
+        <v>-0.1104</v>
       </c>
       <c r="G95" t="n">
-        <v>264.5763</v>
+        <v>276.9699</v>
       </c>
       <c r="H95" t="n">
-        <v>381.9164</v>
+        <v>371.161</v>
       </c>
     </row>
     <row r="96">
@@ -3482,20 +3482,20 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9789</v>
+        <v>0.8891</v>
       </c>
       <c r="F96" t="n">
-        <v>1.5817</v>
+        <v>0.4445</v>
       </c>
       <c r="G96" t="n">
-        <v>91.86360000000001</v>
+        <v>169.7588</v>
       </c>
       <c r="H96" t="n">
-        <v>268.7021</v>
+        <v>262.5188</v>
       </c>
     </row>
     <row r="97">
@@ -3514,20 +3514,20 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.8891</v>
       </c>
       <c r="F97" t="n">
-        <v>1.582</v>
+        <v>0.443</v>
       </c>
       <c r="G97" t="n">
-        <v>92.9584</v>
+        <v>169.6924</v>
       </c>
       <c r="H97" t="n">
-        <v>268.7802</v>
+        <v>262.8693</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9822</v>
+        <v>0.9368</v>
       </c>
       <c r="F98" t="n">
-        <v>1.4552</v>
+        <v>0.527</v>
       </c>
       <c r="G98" t="n">
-        <v>81.31399999999999</v>
+        <v>136.9918</v>
       </c>
       <c r="H98" t="n">
-        <v>237.6991</v>
+        <v>242.2518</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9626</v>
+        <v>0.9267</v>
       </c>
       <c r="F99" t="n">
-        <v>1.4464</v>
+        <v>0.5273</v>
       </c>
       <c r="G99" t="n">
-        <v>107.9401</v>
+        <v>142.4881</v>
       </c>
       <c r="H99" t="n">
-        <v>235.3773</v>
+        <v>242.1701</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9801</v>
+        <v>0.9236</v>
       </c>
       <c r="F100" t="n">
-        <v>1.452</v>
+        <v>0.5193</v>
       </c>
       <c r="G100" t="n">
-        <v>83.2572</v>
+        <v>144.6337</v>
       </c>
       <c r="H100" t="n">
-        <v>236.8634</v>
+        <v>244.2117</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9595</v>
+        <v>0.9334</v>
       </c>
       <c r="F101" t="n">
-        <v>1.455</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>111.5956</v>
+        <v>137.9333</v>
       </c>
       <c r="H101" t="n">
-        <v>237.6393</v>
+        <v>244.9</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9586</v>
+        <v>0.9191</v>
       </c>
       <c r="F102" t="n">
-        <v>1.4652</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="G102" t="n">
-        <v>112.3118</v>
+        <v>147.6157</v>
       </c>
       <c r="H102" t="n">
-        <v>240.2865</v>
+        <v>244.893</v>
       </c>
     </row>
     <row r="103">
@@ -3710,16 +3710,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>1.4579</v>
+        <v>0.5222</v>
       </c>
       <c r="G103" t="n">
-        <v>81.9766</v>
+        <v>90.2411</v>
       </c>
       <c r="H103" t="n">
-        <v>238.4081</v>
+        <v>243.481</v>
       </c>
     </row>
     <row r="104">
@@ -3738,20 +3738,20 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9815</v>
+        <v>0.9578</v>
       </c>
       <c r="F104" t="n">
-        <v>1.4579</v>
+        <v>0.5191</v>
       </c>
       <c r="G104" t="n">
-        <v>83.1315</v>
+        <v>113.6652</v>
       </c>
       <c r="H104" t="n">
-        <v>238.4114</v>
+        <v>244.2704</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9804</v>
+        <v>0.9549</v>
       </c>
       <c r="F105" t="n">
-        <v>1.4516</v>
+        <v>0.5209</v>
       </c>
       <c r="G105" t="n">
-        <v>83.352</v>
+        <v>116.5929</v>
       </c>
       <c r="H105" t="n">
-        <v>236.7661</v>
+        <v>243.8123</v>
       </c>
     </row>
     <row r="106">
@@ -3802,20 +3802,20 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9636</v>
+        <v>0.9633</v>
       </c>
       <c r="F106" t="n">
-        <v>1.4524</v>
+        <v>0.516</v>
       </c>
       <c r="G106" t="n">
-        <v>106.9045</v>
+        <v>108.8289</v>
       </c>
       <c r="H106" t="n">
-        <v>236.9577</v>
+        <v>245.0476</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9604</v>
+        <v>0.921</v>
       </c>
       <c r="F107" t="n">
-        <v>1.4553</v>
+        <v>0.5115</v>
       </c>
       <c r="G107" t="n">
-        <v>110.0998</v>
+        <v>146.1529</v>
       </c>
       <c r="H107" t="n">
-        <v>237.7197</v>
+        <v>246.19</v>
       </c>
     </row>
     <row r="108">
@@ -3870,16 +3870,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9825</v>
+        <v>0.9829</v>
       </c>
       <c r="F108" t="n">
-        <v>1.4654</v>
+        <v>0.548</v>
       </c>
       <c r="G108" t="n">
-        <v>83.64319999999999</v>
+        <v>86.1207</v>
       </c>
       <c r="H108" t="n">
-        <v>240.3379</v>
+        <v>236.8159</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9747</v>
+        <v>0.9696</v>
       </c>
       <c r="F109" t="n">
-        <v>1.422</v>
+        <v>0.5749</v>
       </c>
       <c r="G109" t="n">
-        <v>90.88120000000001</v>
+        <v>101.689</v>
       </c>
       <c r="H109" t="n">
-        <v>228.8701</v>
+        <v>229.6663</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9823</v>
+        <v>0.9804</v>
       </c>
       <c r="F110" t="n">
-        <v>1.444</v>
+        <v>0.5592</v>
       </c>
       <c r="G110" t="n">
-        <v>80.6255</v>
+        <v>87.5491</v>
       </c>
       <c r="H110" t="n">
-        <v>234.7608</v>
+        <v>233.8549</v>
       </c>
     </row>
     <row r="111">
@@ -3966,16 +3966,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9817</v>
+        <v>0.9784</v>
       </c>
       <c r="F111" t="n">
-        <v>1.4383</v>
+        <v>0.5429</v>
       </c>
       <c r="G111" t="n">
-        <v>81.04940000000001</v>
+        <v>88.5461</v>
       </c>
       <c r="H111" t="n">
-        <v>233.2302</v>
+        <v>238.1457</v>
       </c>
     </row>
     <row r="112">
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9826</v>
       </c>
       <c r="F112" t="n">
-        <v>1.4655</v>
+        <v>0.5501</v>
       </c>
       <c r="G112" t="n">
-        <v>83.53700000000001</v>
+        <v>86.2953</v>
       </c>
       <c r="H112" t="n">
-        <v>240.37</v>
+        <v>236.2468</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9745</v>
+        <v>0.9691</v>
       </c>
       <c r="F113" t="n">
-        <v>1.4211</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>91.33159999999999</v>
+        <v>102.186</v>
       </c>
       <c r="H113" t="n">
-        <v>228.6304</v>
+        <v>230.6824</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.977</v>
+        <v>0.9812</v>
       </c>
       <c r="F114" t="n">
-        <v>1.4365</v>
+        <v>0.5598</v>
       </c>
       <c r="G114" t="n">
-        <v>85.42910000000001</v>
+        <v>83.6463</v>
       </c>
       <c r="H114" t="n">
-        <v>232.7535</v>
+        <v>233.6897</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9828</v>
+        <v>0.9811</v>
       </c>
       <c r="F115" t="n">
-        <v>1.4311</v>
+        <v>0.5598</v>
       </c>
       <c r="G115" t="n">
-        <v>79.4413</v>
+        <v>83.4585</v>
       </c>
       <c r="H115" t="n">
-        <v>231.3174</v>
+        <v>233.6871</v>
       </c>
     </row>
     <row r="116">
@@ -4122,20 +4122,20 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.9304</v>
+        <v>0.8072</v>
       </c>
       <c r="F116" t="n">
-        <v>2.025</v>
+        <v>-0.0274</v>
       </c>
       <c r="G116" t="n">
-        <v>180.5158</v>
+        <v>254.3502</v>
       </c>
       <c r="H116" t="n">
-        <v>356.6879</v>
+        <v>357.0294</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8527</v>
+        <v>0.83</v>
       </c>
       <c r="F117" t="n">
-        <v>2.0134</v>
+        <v>-0.025</v>
       </c>
       <c r="G117" t="n">
-        <v>226.2557</v>
+        <v>245.7925</v>
       </c>
       <c r="H117" t="n">
-        <v>354.6575</v>
+        <v>356.6116</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9804</v>
+        <v>0.9549</v>
       </c>
       <c r="F118" t="n">
-        <v>1.4516</v>
+        <v>0.5209</v>
       </c>
       <c r="G118" t="n">
-        <v>83.352</v>
+        <v>116.5929</v>
       </c>
       <c r="H118" t="n">
-        <v>236.7661</v>
+        <v>243.8123</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9745</v>
+        <v>0.9691</v>
       </c>
       <c r="F119" t="n">
-        <v>1.4211</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="G119" t="n">
-        <v>91.33159999999999</v>
+        <v>102.186</v>
       </c>
       <c r="H119" t="n">
-        <v>228.6304</v>
+        <v>230.6824</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.8964</v>
+        <v>0.8822</v>
       </c>
       <c r="F120" t="n">
-        <v>1.5176</v>
+        <v>0.4467</v>
       </c>
       <c r="G120" t="n">
-        <v>162.0505</v>
+        <v>172.2939</v>
       </c>
       <c r="H120" t="n">
-        <v>253.4733</v>
+        <v>262.001</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.8964</v>
+        <v>0.8822</v>
       </c>
       <c r="F121" t="n">
-        <v>1.5176</v>
+        <v>0.4467</v>
       </c>
       <c r="G121" t="n">
-        <v>162.0505</v>
+        <v>172.2939</v>
       </c>
       <c r="H121" t="n">
-        <v>253.4733</v>
+        <v>262.001</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9366</v>
+        <v>0.9244</v>
       </c>
       <c r="F122" t="n">
-        <v>1.4611</v>
+        <v>0.4872</v>
       </c>
       <c r="G122" t="n">
-        <v>134.4979</v>
+        <v>143.5156</v>
       </c>
       <c r="H122" t="n">
-        <v>239.2284</v>
+        <v>252.2242</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9823</v>
+        <v>0.969</v>
       </c>
       <c r="F123" t="n">
-        <v>1.4212</v>
+        <v>0.5714</v>
       </c>
       <c r="G123" t="n">
-        <v>78.7385</v>
+        <v>102.2252</v>
       </c>
       <c r="H123" t="n">
-        <v>228.6513</v>
+        <v>230.5903</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9816</v>
+        <v>0.9809</v>
       </c>
       <c r="F124" t="n">
-        <v>1.4339</v>
+        <v>0.5617</v>
       </c>
       <c r="G124" t="n">
-        <v>80.99630000000001</v>
+        <v>85.4068</v>
       </c>
       <c r="H124" t="n">
-        <v>232.0748</v>
+        <v>233.1827</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9442</v>
+        <v>0.8871</v>
       </c>
       <c r="F125" t="n">
-        <v>1.5909</v>
+        <v>0.4344</v>
       </c>
       <c r="G125" t="n">
-        <v>133.9448</v>
+        <v>176.1015</v>
       </c>
       <c r="H125" t="n">
-        <v>270.8245</v>
+        <v>264.8939</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9823</v>
+        <v>0.9721</v>
       </c>
       <c r="F126" t="n">
-        <v>1.51</v>
+        <v>0.4694</v>
       </c>
       <c r="G126" t="n">
-        <v>83.3531</v>
+        <v>98.20650000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>251.5898</v>
+        <v>256.5743</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8561</v>
+        <v>0.8399</v>
       </c>
       <c r="F127" t="n">
-        <v>2.0637</v>
+        <v>-0.0623</v>
       </c>
       <c r="G127" t="n">
-        <v>223.916</v>
+        <v>236.7105</v>
       </c>
       <c r="H127" t="n">
-        <v>363.3514</v>
+        <v>363.0398</v>
       </c>
     </row>
     <row r="128">
@@ -4506,20 +4506,20 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9811</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>1.5095</v>
+        <v>0.4692</v>
       </c>
       <c r="G128" t="n">
-        <v>83.87</v>
+        <v>98.5587</v>
       </c>
       <c r="H128" t="n">
-        <v>251.4823</v>
+        <v>256.6175</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9821</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>1.5206</v>
+        <v>0.471</v>
       </c>
       <c r="G129" t="n">
-        <v>81.5492</v>
+        <v>99.50369999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>254.2119</v>
+        <v>256.1789</v>
       </c>
     </row>
     <row r="130">
@@ -4570,20 +4570,20 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9808</v>
+        <v>0.9729</v>
       </c>
       <c r="F130" t="n">
-        <v>1.5056</v>
+        <v>0.4612</v>
       </c>
       <c r="G130" t="n">
-        <v>85.2962</v>
+        <v>99.0239</v>
       </c>
       <c r="H130" t="n">
-        <v>250.5</v>
+        <v>258.5465</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9809</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>1.5058</v>
+        <v>0.4689</v>
       </c>
       <c r="G131" t="n">
-        <v>84.0433</v>
+        <v>101.1504</v>
       </c>
       <c r="H131" t="n">
-        <v>250.5492</v>
+        <v>256.6916</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9825</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>1.4984</v>
+        <v>0.4795</v>
       </c>
       <c r="G132" t="n">
-        <v>82.889</v>
+        <v>98.0621</v>
       </c>
       <c r="H132" t="n">
-        <v>248.7274</v>
+        <v>254.1146</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9819</v>
+        <v>0.973</v>
       </c>
       <c r="F133" t="n">
-        <v>1.4976</v>
+        <v>0.4812</v>
       </c>
       <c r="G133" t="n">
-        <v>82.7163</v>
+        <v>98.95010000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>248.52</v>
+        <v>253.7059</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9807</v>
+        <v>0.9715</v>
       </c>
       <c r="F134" t="n">
-        <v>1.5025</v>
+        <v>0.4852</v>
       </c>
       <c r="G134" t="n">
-        <v>84.7068</v>
+        <v>98.3476</v>
       </c>
       <c r="H134" t="n">
-        <v>249.7361</v>
+        <v>252.7165</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9815</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>1.5078</v>
+        <v>0.4765</v>
       </c>
       <c r="G135" t="n">
-        <v>83.97029999999999</v>
+        <v>98.7718</v>
       </c>
       <c r="H135" t="n">
-        <v>251.0583</v>
+        <v>254.8572</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.9816</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>1.5049</v>
+        <v>0.4699</v>
       </c>
       <c r="G136" t="n">
-        <v>83.5458</v>
+        <v>99.4885</v>
       </c>
       <c r="H136" t="n">
-        <v>250.333</v>
+        <v>256.4571</v>
       </c>
     </row>
     <row r="137">
@@ -4794,20 +4794,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9611</v>
+        <v>0.9755</v>
       </c>
       <c r="F137" t="n">
-        <v>1.4675</v>
+        <v>0.5248</v>
       </c>
       <c r="G137" t="n">
-        <v>109.0518</v>
+        <v>93.9509</v>
       </c>
       <c r="H137" t="n">
-        <v>240.8848</v>
+        <v>242.8103</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9701</v>
+        <v>0.973</v>
       </c>
       <c r="F138" t="n">
-        <v>1.4745</v>
+        <v>0.5184</v>
       </c>
       <c r="G138" t="n">
-        <v>99.7942</v>
+        <v>96.291</v>
       </c>
       <c r="H138" t="n">
-        <v>242.6957</v>
+        <v>244.4435</v>
       </c>
     </row>
     <row r="139">
@@ -4858,20 +4858,20 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9754</v>
       </c>
       <c r="F139" t="n">
-        <v>1.4717</v>
+        <v>0.5312</v>
       </c>
       <c r="G139" t="n">
-        <v>99.108</v>
+        <v>93.3587</v>
       </c>
       <c r="H139" t="n">
-        <v>241.9638</v>
+        <v>241.1829</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9764</v>
       </c>
       <c r="F140" t="n">
-        <v>1.4084</v>
+        <v>0.5784</v>
       </c>
       <c r="G140" t="n">
-        <v>91.4914</v>
+        <v>86.3759</v>
       </c>
       <c r="H140" t="n">
-        <v>225.1426</v>
+        <v>228.6994</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9801</v>
+        <v>0.9768</v>
       </c>
       <c r="F141" t="n">
-        <v>1.4345</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="G141" t="n">
-        <v>82.8646</v>
+        <v>88.3947</v>
       </c>
       <c r="H141" t="n">
-        <v>232.2176</v>
+        <v>233.1043</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9701</v>
+        <v>0.973</v>
       </c>
       <c r="F142" t="n">
-        <v>1.4745</v>
+        <v>0.5184</v>
       </c>
       <c r="G142" t="n">
-        <v>99.7942</v>
+        <v>96.291</v>
       </c>
       <c r="H142" t="n">
-        <v>242.6957</v>
+        <v>244.4435</v>
       </c>
     </row>
     <row r="143">
@@ -4986,20 +4986,20 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9706</v>
+        <v>0.9742</v>
       </c>
       <c r="F143" t="n">
-        <v>1.4415</v>
+        <v>0.5196</v>
       </c>
       <c r="G143" t="n">
-        <v>95.77119999999999</v>
+        <v>94.8809</v>
       </c>
       <c r="H143" t="n">
-        <v>234.0818</v>
+        <v>244.1259</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9745</v>
       </c>
       <c r="F144" t="n">
-        <v>1.4611</v>
+        <v>0.5272</v>
       </c>
       <c r="G144" t="n">
-        <v>96.3704</v>
+        <v>92.04430000000001</v>
       </c>
       <c r="H144" t="n">
-        <v>239.2396</v>
+        <v>242.1974</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9801</v>
+        <v>0.9768</v>
       </c>
       <c r="F145" t="n">
-        <v>1.4345</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="G145" t="n">
-        <v>82.8646</v>
+        <v>88.3947</v>
       </c>
       <c r="H145" t="n">
-        <v>232.2176</v>
+        <v>233.1043</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8397</v>
+        <v>0.8626</v>
       </c>
       <c r="F146" t="n">
-        <v>2.0536</v>
+        <v>-0.0544</v>
       </c>
       <c r="G146" t="n">
-        <v>232.145</v>
+        <v>223.0748</v>
       </c>
       <c r="H146" t="n">
-        <v>361.626</v>
+        <v>361.6889</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.8375</v>
+        <v>0.864</v>
       </c>
       <c r="F147" t="n">
-        <v>2.0546</v>
+        <v>-0.0528</v>
       </c>
       <c r="G147" t="n">
-        <v>232.6473</v>
+        <v>222.5496</v>
       </c>
       <c r="H147" t="n">
-        <v>361.7929</v>
+        <v>361.4161</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8615</v>
       </c>
       <c r="F148" t="n">
-        <v>2.0519</v>
+        <v>-0.0492</v>
       </c>
       <c r="G148" t="n">
-        <v>232.3384</v>
+        <v>223.3674</v>
       </c>
       <c r="H148" t="n">
-        <v>361.3305</v>
+        <v>360.7966</v>
       </c>
     </row>
     <row r="149">
@@ -5182,16 +5182,16 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8649</v>
+        <v>0.8628</v>
       </c>
       <c r="F149" t="n">
-        <v>2.0488</v>
+        <v>-0.0493</v>
       </c>
       <c r="G149" t="n">
-        <v>221.077</v>
+        <v>223.1997</v>
       </c>
       <c r="H149" t="n">
-        <v>360.8039</v>
+        <v>360.8055</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.836</v>
+        <v>0.8621</v>
       </c>
       <c r="F150" t="n">
-        <v>2.062</v>
+        <v>-0.0588</v>
       </c>
       <c r="G150" t="n">
-        <v>231.8782</v>
+        <v>223.3248</v>
       </c>
       <c r="H150" t="n">
-        <v>363.0733</v>
+        <v>362.4381</v>
       </c>
     </row>
     <row r="151">
@@ -5246,16 +5246,16 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8386</v>
+        <v>0.8431</v>
       </c>
       <c r="F151" t="n">
-        <v>2.0544</v>
+        <v>-0.0576</v>
       </c>
       <c r="G151" t="n">
-        <v>230.8075</v>
+        <v>236.2737</v>
       </c>
       <c r="H151" t="n">
-        <v>361.7634</v>
+        <v>362.2287</v>
       </c>
     </row>
     <row r="152">
@@ -5274,20 +5274,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8406</v>
+        <v>0.8563</v>
       </c>
       <c r="F152" t="n">
-        <v>2.0526</v>
+        <v>-0.0608</v>
       </c>
       <c r="G152" t="n">
-        <v>230.8476</v>
+        <v>226.9799</v>
       </c>
       <c r="H152" t="n">
-        <v>361.4492</v>
+        <v>362.7865</v>
       </c>
     </row>
     <row r="153">
@@ -5306,20 +5306,20 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.8605</v>
       </c>
       <c r="F153" t="n">
-        <v>2.0592</v>
+        <v>-0.0591</v>
       </c>
       <c r="G153" t="n">
-        <v>232.9255</v>
+        <v>225.9673</v>
       </c>
       <c r="H153" t="n">
-        <v>362.5899</v>
+        <v>362.4969</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8344</v>
+        <v>0.8601</v>
       </c>
       <c r="F154" t="n">
-        <v>2.0497</v>
+        <v>-0.0544</v>
       </c>
       <c r="G154" t="n">
-        <v>231.8489</v>
+        <v>223.3881</v>
       </c>
       <c r="H154" t="n">
-        <v>360.9492</v>
+        <v>361.6892</v>
       </c>
     </row>
     <row r="155">
@@ -5374,16 +5374,16 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8764</v>
+        <v>0.8986</v>
       </c>
       <c r="F155" t="n">
-        <v>2.0398</v>
+        <v>-0.0213</v>
       </c>
       <c r="G155" t="n">
-        <v>228.2008</v>
+        <v>229.9854</v>
       </c>
       <c r="H155" t="n">
-        <v>359.2558</v>
+        <v>355.9601</v>
       </c>
     </row>
     <row r="156">
@@ -5406,16 +5406,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.8505</v>
+        <v>0.8741</v>
       </c>
       <c r="F156" t="n">
-        <v>2.0454</v>
+        <v>-0.0204</v>
       </c>
       <c r="G156" t="n">
-        <v>238.8687</v>
+        <v>242.3478</v>
       </c>
       <c r="H156" t="n">
-        <v>360.2218</v>
+        <v>355.8042</v>
       </c>
     </row>
     <row r="157">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8759</v>
+        <v>0.8905</v>
       </c>
       <c r="F157" t="n">
-        <v>2.0393</v>
+        <v>-0.0217</v>
       </c>
       <c r="G157" t="n">
-        <v>227.3839</v>
+        <v>231.6702</v>
       </c>
       <c r="H157" t="n">
-        <v>359.1725</v>
+        <v>356.0377</v>
       </c>
     </row>
     <row r="158">
@@ -5466,20 +5466,20 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8742</v>
+        <v>0.9069</v>
       </c>
       <c r="F158" t="n">
-        <v>1.9697</v>
+        <v>0.038</v>
       </c>
       <c r="G158" t="n">
-        <v>230.0989</v>
+        <v>221.7073</v>
       </c>
       <c r="H158" t="n">
-        <v>346.9333</v>
+        <v>345.4795</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.9776</v>
       </c>
       <c r="F159" t="n">
-        <v>1.4659</v>
+        <v>0.4883</v>
       </c>
       <c r="G159" t="n">
-        <v>84.96429999999999</v>
+        <v>93.41589999999999</v>
       </c>
       <c r="H159" t="n">
-        <v>240.4694</v>
+        <v>251.9576</v>
       </c>
     </row>
     <row r="160">
@@ -5530,20 +5530,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8462</v>
+        <v>0.8792</v>
       </c>
       <c r="F160" t="n">
-        <v>2.0585</v>
+        <v>-0.0789</v>
       </c>
       <c r="G160" t="n">
-        <v>242.6177</v>
+        <v>224.1904</v>
       </c>
       <c r="H160" t="n">
-        <v>362.46</v>
+        <v>365.8635</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8581</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="F161" t="n">
-        <v>2.0528</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="G161" t="n">
-        <v>231.0193</v>
+        <v>222.7697</v>
       </c>
       <c r="H161" t="n">
-        <v>361.4839</v>
+        <v>364.4427</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9609</v>
+        <v>0.9768</v>
       </c>
       <c r="F162" t="n">
-        <v>1.4778</v>
+        <v>0.4867</v>
       </c>
       <c r="G162" t="n">
-        <v>109.176</v>
+        <v>93.67319999999999</v>
       </c>
       <c r="H162" t="n">
-        <v>243.5304</v>
+        <v>252.3514</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9712</v>
+        <v>0.9765</v>
       </c>
       <c r="F163" t="n">
-        <v>1.4958</v>
+        <v>0.4994</v>
       </c>
       <c r="G163" t="n">
-        <v>96.669</v>
+        <v>92.4213</v>
       </c>
       <c r="H163" t="n">
-        <v>248.084</v>
+        <v>249.2186</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9712</v>
+        <v>0.9765</v>
       </c>
       <c r="F164" t="n">
-        <v>1.4075</v>
+        <v>0.5756</v>
       </c>
       <c r="G164" t="n">
-        <v>91.63760000000001</v>
+        <v>86.535</v>
       </c>
       <c r="H164" t="n">
-        <v>224.8966</v>
+        <v>229.4529</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9442</v>
+        <v>0.8871</v>
       </c>
       <c r="F165" t="n">
-        <v>1.5909</v>
+        <v>0.4344</v>
       </c>
       <c r="G165" t="n">
-        <v>133.9448</v>
+        <v>176.1015</v>
       </c>
       <c r="H165" t="n">
-        <v>270.8245</v>
+        <v>264.8939</v>
       </c>
     </row>
     <row r="166">
@@ -5726,16 +5726,16 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.7458</v>
+        <v>0.7009</v>
       </c>
       <c r="F166" t="n">
-        <v>2.1736</v>
+        <v>-0.1164</v>
       </c>
       <c r="G166" t="n">
-        <v>265.7293</v>
+        <v>276.2168</v>
       </c>
       <c r="H166" t="n">
-        <v>381.6626</v>
+        <v>372.1689</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9722</v>
+        <v>0.9791</v>
       </c>
       <c r="F167" t="n">
-        <v>1.4</v>
+        <v>0.5491</v>
       </c>
       <c r="G167" t="n">
-        <v>92.24890000000001</v>
+        <v>89.0827</v>
       </c>
       <c r="H167" t="n">
-        <v>222.8232</v>
+        <v>236.5276</v>
       </c>
     </row>
     <row r="168">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9791</v>
+        <v>0.9779</v>
       </c>
       <c r="F168" t="n">
-        <v>1.3845</v>
+        <v>0.6081</v>
       </c>
       <c r="G168" t="n">
-        <v>77.5085</v>
+        <v>84.25539999999999</v>
       </c>
       <c r="H168" t="n">
-        <v>218.4699</v>
+        <v>220.5138</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9534</v>
+        <v>0.9285</v>
       </c>
       <c r="F169" t="n">
-        <v>1.4908</v>
+        <v>0.4891</v>
       </c>
       <c r="G169" t="n">
-        <v>122.3717</v>
+        <v>144.724</v>
       </c>
       <c r="H169" t="n">
-        <v>246.8227</v>
+        <v>251.7774</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9804</v>
+        <v>0.9832</v>
       </c>
       <c r="F170" t="n">
-        <v>1.4574</v>
+        <v>0.5162</v>
       </c>
       <c r="G170" t="n">
-        <v>82.3142</v>
+        <v>85.0116</v>
       </c>
       <c r="H170" t="n">
-        <v>238.2644</v>
+        <v>244.9964</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9839</v>
+        <v>0.9747</v>
       </c>
       <c r="F171" t="n">
-        <v>1.4223</v>
+        <v>0.6133</v>
       </c>
       <c r="G171" t="n">
-        <v>76.9773</v>
+        <v>90.19929999999999</v>
       </c>
       <c r="H171" t="n">
-        <v>228.941</v>
+        <v>219.0324</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9683</v>
+        <v>0.9627</v>
       </c>
       <c r="F172" t="n">
-        <v>1.4577</v>
+        <v>0.5163</v>
       </c>
       <c r="G172" t="n">
-        <v>98.7353</v>
+        <v>108.2187</v>
       </c>
       <c r="H172" t="n">
-        <v>238.3591</v>
+        <v>244.9673</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/trans.alpha.carotene/RANDOMSEARCH_DETAILS_trans.alpha.carotene.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2308,7 +2308,7 @@
         <v>-0.09320000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>241.9526</v>
+        <v>241.9658</v>
       </c>
       <c r="H59" t="n">
         <v>368.2765</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -2372,7 +2372,7 @@
         <v>-0.08989999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>241.1527</v>
+        <v>241.149</v>
       </c>
       <c r="H61" t="n">
         <v>367.7335</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E169" t="n">
